--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L79"/>
+  <dimension ref="A1:L80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -571,7 +571,6 @@
           <t>watchdog 자동 재시작 + Slack 원격 제어 추가</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>watchdog 자동 재시작 + Slack 원격 제어 추가</t>
@@ -687,7 +686,6 @@
           <t>Bridge 모드 + 오류 감지 대체 투입 + load_dotenv override</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Bridge 모드 + 오류 감지 대체 투입 + load_dotenv override</t>
@@ -803,10 +801,9 @@
           <t>!stop 강제 중단 + 코딩 모드 개선 + 작업 취소 시스템</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>!stop 강제 중단 + 코딩 모드 개선 + 작업 취소 시스템</t>
+          <t>!stop 강제 중단 + 코딩 모드 개선 + 작업 취소 시</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -859,7 +856,6 @@
           <t>Claude 응답에 토큰 사용량 표시 (k 단위)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>Claude 응답에 토큰 사용량 표시 (k 단위)</t>
@@ -915,7 +911,6 @@
           <t>코딩 모드 스트리밍 진행 표시 + idle 타임아웃</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>코딩 모드 스트리밍 진행 표시 + idle 타임아웃</t>
@@ -1031,7 +1026,6 @@
           <t>코딩 채널 followup 에이전트 자동 선택</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>코딩 채널 followup 에이전트 자동 선택</t>
@@ -1087,7 +1081,6 @@
           <t>전 에이전트 스트리밍 진행 표시 + 복수 에이전트 동시 지정</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>전 에이전트 스트리밍 진행 표시 + 복수 에이전트 동시 지정</t>
@@ -1323,7 +1316,6 @@
           <t>코딩 채널 병렬 모드 지원</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>코딩 채널 병렬 모드 지원</t>
@@ -1439,7 +1431,6 @@
           <t>Claude 작업 내용 실시간 표시 + Codex/Gemini 경과 시간</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>Claude 작업 내용 실시간 표시 + Codex/Gemini 경과 시간</t>
@@ -1495,7 +1486,6 @@
           <t>모든 에이전트 작업 내용 실시간 표시 통일</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>모든 에이전트 작업 내용 실시간 표시 통일</t>
@@ -1551,7 +1541,6 @@
           <t>봇 재시작 시 모든 채널에 작업 중단 알림</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>봇 재시작 시 모든 채널에 작업 중단 알림</t>
@@ -1607,7 +1596,6 @@
           <t>모든 에이전트 경과 시간 + 내용 하이브리드 표시</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>모든 에이전트 경과 시간 + 내용 하이브리드 표시</t>
@@ -1723,7 +1711,6 @@
           <t>봇 재시작 시 진행 중이던 스레드에 중단 알림</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>봇 재시작 시 진행 중이던 스레드에 중단 알림</t>
@@ -1899,7 +1886,6 @@
           <t>Codex --full-auto 모드로 셸 실행 권한 부여</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>Codex --full-auto 모드로 셸 실행 권한 부여</t>
@@ -1955,7 +1941,6 @@
           <t>Gemini -y (YOLO) 모드로 도구 자동 승인</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>Gemini -y (YOLO) 모드로 도구 자동 승인</t>
@@ -2251,7 +2236,6 @@
           <t>병렬 모드 완료 후 Codex가 최종 보고서 작성</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>병렬 모드 완료 후 Codex가 최종 보고서 작성</t>
@@ -2307,7 +2291,6 @@
           <t>파이프라인 모드 최종 보고서도 Codex가 작성</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>파이프라인 모드 최종 보고서도 Codex가 작성</t>
@@ -2423,7 +2406,6 @@
           <t>병렬 모드에 대체 에이전트 투입 추가</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>병렬 모드에 대체 에이전트 투입 추가</t>
@@ -3199,7 +3181,6 @@
           <t>kill_process_tree를 process.py로 통합</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>kill_process_tree를 process.py로 통합</t>
@@ -3255,7 +3236,6 @@
           <t>security.py에 경로 화이트리스트 검증 추가</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>security.py에 경로 화이트리스트 검증 추가</t>
@@ -3311,7 +3291,6 @@
           <t>bridge paths를 .env로 외부화 + env 필터링</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>bridge paths를 .env로 외부화 + env 필터링</t>
@@ -4207,7 +4186,6 @@
           <t>토론 합의 후 통합 답변 생성</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>토론 합의 후 통합 답변 생성</t>
@@ -4263,7 +4241,6 @@
           <t>watchdog 복원력 강화 + watchdog_guard 추가</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>watchdog 복원력 강화 + watchdog_guard 추가</t>
@@ -4499,7 +4476,6 @@
           <t>Gemini primary를 gemini-2.5-flash-lite로 교체 + semaphore 완화</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>Gemini primary를 gemini-2.5-flash-lite로 교체 + semaphore 완화</t>
@@ -4555,7 +4531,6 @@
           <t>Gemini primary를 gemini-3-flash-preview로 교체</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>Gemini primary를 gemini-3-flash-preview로 교체</t>
@@ -5031,7 +5006,6 @@
           <t>부팅 시 CLI 헬스체크 (claude/codex/gemini --version)</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>부팅 시 CLI 헬스체크 (claude/codex/gemini --version)</t>
@@ -5065,6 +5039,62 @@
       <c r="L79" t="inlineStr">
         <is>
           <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Slack 첨부 이미지 분석 지원 (Claude/Gemini Vision)</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Slack 메시지에 첨부된 이미지(image/* MIME)를 봇 토큰으로 다운로드해 base64 인코딩 후, Claude(Anthropic SDK), Gemini(google-genai SDK) Vision 호출에 전달. Codex는 멀티모달 미지원이라 prompt 끝에 "이미지 N장 첨부됨" 노트만 추가. Debate / Coding / Bridge 3개 모드 모두 적용. 부팅 시 비전 SDK·키 헬스체크 추가.</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>기존 봇 파이프라인이 event["text"]만 추출하고 event["files"]를 무시했고, 모든 ask 시그니처가 prompt: str 단일이었음. 사용자가 차트 이미지를 첨부해도 분석 불가, 일부 에이전트(Gemini)는 검색 결과로 환각 분석을 하는 사고가 발생. agents/base.py·claude.py·gemini.py·codex.py 시그니처 확장 + slack_files.py 신규 + 모드별 호출 사이트 업데이트로 해결.</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>backend (slack_bot.py, agents/*, modes/*, slack_files.py 신규). anthropic, google-genai 의존성 추가.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>v0.5.1</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>v0.6.0</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Major</t>
         </is>
       </c>
     </row>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L80"/>
+  <dimension ref="A1:L81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5061,7 +5061,6 @@
           <t>Slack 첨부 이미지 분석 지원 (Claude/Gemini Vision)</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>Slack 메시지에 첨부된 이미지(image/* MIME)를 봇 토큰으로 다운로드해 base64 인코딩 후, Claude(Anthropic SDK), Gemini(google-genai SDK) Vision 호출에 전달. Codex는 멀티모달 미지원이라 prompt 끝에 "이미지 N장 첨부됨" 노트만 추가. Debate / Coding / Bridge 3개 모드 모두 적용. 부팅 시 비전 SDK·키 헬스체크 추가.</t>
@@ -5093,6 +5092,66 @@
         </is>
       </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>이미지 첨부 분석을 SDK 직호출로 잘못 구현 → CLI prompt 첨부로 정정</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>사용자가 Claude Code / Codex CLI / Gemini CLI 를 OAuth 구독 모드(API 키 없음)로 운영 중. Google AI Pro 구독, Anthropic/OpenAI 구독 OAuth 로그인 상태.</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>슬랙 채널에 차트 이미지 첨부 후 봇에 분석 요청 → 봇이 "anthropic SDK 미설치" 또는 "ANTHROPIC_API_KEY 환경변수 없음" 에러 반환. v0.6.0 도입 직후 이미지 첨부 분석 자체가 동작 불가 상태.</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>v0.6.0 에서 비전 호출을 Anthropic Python SDK + google-genai SDK 직호출로 구현했는데, 이는 사용자 운영 모델과 불일치(API 키 강요). CLI 자체가 OAuth 로 multimodal 입력을 처리할 수 있는데 그 경로를 무시함. 정정: Slack 첨부 이미지를 임시 파일로 저장 + 절대경로를 각 CLI 의 첨부 syntax 로 prompt 에 끼워 호출 (Claude: prompt 안에 경로 + Read 도구, Gemini: @&lt;path&gt;, Codex: prompt 안에 경로 + read 도구). SDK 의존성(anthropic, google-genai) 제거, 비전 헬스체크 제거. 임시 디렉토리는 작업 종료 후 shutil.rmtree 로 정리.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>backend (agents/claude.py, agents/gemini.py, agents/codex.py, slack_files.py, slack_bot.py, requirements.txt). 신규 단위 테스트 142건 통과 (이전 139건 대비 +3).</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>v0.6.0</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>v0.6.1</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t>Major</t>
         </is>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5157,6 +5157,66 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>텍스트+이미지 한 번에 입력 시 봇 무반응</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1) Slack 채널에 텍스트와 이미지를 한 메시지로 첨부 후 전송 2) 봇 무반응</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>slack_bot.handle_message 가 event.get(subtype) 가 truthy 면 즉시 return 하여 Slack 의 file_share subtype(첨부 동반 메시지) 이 통째로 차단됨. _PROCESS_SUBTYPES = {None, file_share, thread_broadcast} 화이트리스트와 should_process_event predicate 도입으로 정정. 단위 테스트 10건 추가.</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Debate/Coding/Bridge 3개 모드의 모든 첨부 동반 메시지(텍스트+이미지, 이미지 단독)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>v0.6.0 (2026-05-08)</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>v0.6.2 (2026-05-08)</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L82"/>
+  <dimension ref="A1:L86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5217,6 +5217,246 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Claude 이미지 첨부 시 readline 64KB 한계로 항상 실패</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>1) Slack 채널에 텍스트+이미지 첨부 메시지 전송 2) Claude 응답이 매번 [Claude] 오류: Separator is not found, and chunk exceed the limit 으로 끝남</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>asyncio proc.stdout.readline() 기본 limit 이 64KB 인데 Claude Code 가 Read 도구로 이미지를 읽으면 user/tool_result 블록 한 줄이 64KB 를 넘겨 LimitOverrunError 발생. _run_cli / ask_with_progress 양쪽에 limit=_STREAM_LINE_LIMIT (16MB) 전달로 해결.</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Debate/Coding/Bridge 3개 모드의 모든 멀티모달(이미지 첨부) 입력에서 Claude 에이전트</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>v0.6.0 (2026-05-08)</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>v0.6.3 (2026-05-09)</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Codex CLI --full-auto deprecation 경고가 응답 본문에 누출</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>1) Codex 가 실행되는 모든 질문 2) 응답 머리 또는 중간에 warning: `--full-auto` is deprecated; use `--sandbox workspace-write` instead. 그대로 출력</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Codex CLI 0.129 부터 --full-auto 가 deprecated 되어 stdout 첫 줄로 경고를 찍음. _build_cmd 의 --full-auto 를 -s workspace-write 로 교체하고, 방어선으로 _CODEX_DEPRECATION_LINE 정규식(^\s*warning:\s+`--&lt;flag&gt;`\s+is\s+deprecated)을 노이즈 필터에 추가. 일반 본문의 deprecation 언급은 보존.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>모든 모드의 Codex/Codex-B 응답</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>v0.5.0 (2026-04-13, Codex CLI 0.129 업그레이드 시점)</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>v0.6.3 (2026-05-09)</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Gemini CLI Ripgrep 폴백 안내가 응답 본문에 누출</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1) Gemini 응답 머리에 Ripgrep is not available. Falling back to GrepTool. 그대로 출력</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Windows 등 ripgrep 미설치 환경에서 Gemini CLI 가 매 호출마다 stdout 첫 줄로 폴백 안내를 찍는데 _NOISE_KEYWORDS 에 누락되어 있었음. _clean_output / _run_progress_once 양쪽에 키워드 추가.</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>모든 모드의 Gemini 응답 (Windows)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>v0.4.0 (2026-04-10, 초기 Gemini 도입 시점)</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>v0.6.3 (2026-05-09)</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Gemini 차트 이미지 종목 오인 방지 가드</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Gemini 가 차트 이미지를 분석할 때 종목명/티커/현재가를 분석 시작 전에 텍스트로 명시하고, 신뢰도가 낮으면 식별 불확실 로 표기하도록 prompt 머리에 가드 추가.</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Gemini-3-flash-preview 가 현대자동차 차트를 토스로 오인하는 등 vision 식별이 종종 빗나가, 후속 라운드의 합의 정정 단계에 기대지 않고 첫 응답부터 잘못된 전제를 줄이기 위함.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Debate/Coding/Bridge 의 Gemini 멀티모달 입력</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>v0.6.0 (2026-05-08)</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>v0.6.3 (2026-05-09)</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L86"/>
+  <dimension ref="A1:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5457,6 +5457,71 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>코딩 모드 Phase 1 게이트: Claude 코드 완성 전 Codex/Gemini 자동 진입 차단</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>코딩 모드 사용 (CODING_CHANNEL_ID 채널), Phase 1 Claude 응답에 코드 없이 사용자에게 되묻는 질문만 있는 경우</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1. 코딩 채널에 모호한 요청 (예: "커플 웹사이트 만들고 싶어 기획부터")
+2. Phase 1 Claude 가 요구사항 질문으로 응답
+3. 봇이 Claude 응답을 코드로 간주하여 Phase 2 Codex 리뷰 즉시 시작
+4. Codex 가 엉뚱한 stockradar stacktrace 컨텍스트 출력 (277초)
+5. Phase 3 Gemini 는 도달도 못 하고 응답 없음</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>원인: modes/coding.py start() 가 Phase 1 → 2 → 3 무조건 순차 진행. Claude 가 코드 대신 질문으로 응답할 수 있다는 케이스 미처리.
+수정: AWAIT_USER_PATTERN 태그 + 모듈 전역 _PENDING_THREADS dict + threading.Lock + _INFLIGHT_PHASE1 set 으로 Phase 1 게이트 도입. start() 가 태그 감지 시 pending 등록 후 Phase 2/3 호출 없이 종료. followup 에서 사용자 답변 받아 Claude 재호출, 응답에 태그 사라지면 _run_review_and_test() 자동 호출. fenced code block 오탐 방지, UUID sentinel, image 병합 dedup, cancel pending 정리 포함.</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>CodingMode (start/followup) - 모호한 요구사항 + 이미지 첨부 + 동시 followup 시나리오 전반</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>v0.6.3</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>v0.6.4</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L87"/>
+  <dimension ref="A1:L93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5522,6 +5522,369 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>토론 교착 감지(_is_stalemate) 사실상 미발동으로 합의 실패 시 최대 라운드까지 낭비</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>3개 에이전트가 전원 합의(agree=true 3)에 도달하지 못하는 토론</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1. 토론 시작
+2. 2명만 agree=true, 1명 지속 불일치(교착)
+3. _is_stalemate가 메시지 앞 100자 문자열 set 비교라 거의 매칭 안 됨
+4. MAX_DEBATE_ROUNDS(10)까지 불필요하게 진행</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>원인: 앞 100자 일치 휴리스틱은 매 라운드 도입부가 달라 overlap&gt;=2가 사실상 불가. 수정: 라운드별 {agrees,diverged} 스냅샷 기반 재설계(최근 2라운드 정체+발산 시 교착), 시그니처 history-&gt;round_history 변경</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>DebateMode.start/followup 종료 판정, 토론 비용/지연</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>v0.6.4</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>v0.7.0</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>백업 풀 비대칭 + 이중 장애 시 에이전트 다양성 붕괴 및 동일 인스턴스 중복</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Codex/Gemini 순차 또는 동시 장애(타임아웃/429)</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>1. Codex 장애 -&gt; Claude-B 교체
+2. Gemini 장애 -&gt; Claude-B 교체
+3. 살아있는 에이전트가 Claude/Claude-B/Claude-B 동일 모델 3중 -&gt; 교차검증 무의미
+4. 동적 선택이 이미 live인 백업 인스턴스 재선택 시 동일 객체 중복</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>원인: 정적 매핑이 Codex/Gemini 모두 Claude-B로 수렴, Gemini 계열 백업 부재. 수정: GeminiBackupAgent 신설 + base_family 속성 + 실패/생존 계열 회피 동적 선택, 이미 live인 인스턴스는 후보 제외(없으면 풀 폴백)</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>agents 백업 교체 로직, 교차검증 다양성</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>v0.6.4</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>v0.7.0</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>_parse_consensus JSON 파싱 실패 시 무음 None 반환으로 합의 누락</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>에이전트가 CONSENSUS JSON을 trailing comma/콤마 누락 등 미세 깨진 형태로 출력</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1. 응답 말미 CONSENSUS JSON에 trailing comma 등 경미한 오류
+2. json.loads 실패
+3. 조용히 None 반환 -&gt; 해당 라운드 합의 미집계
+4. 토론 불필요 연장 또는 통합문 부실</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>원인: 단일 json.loads 후 except에서 무음 None(로깅/복구 없음). 수정: salvage 단계화(trailing comma 제거 재시도 -&gt; agree/summary 정규식 추출) + 실패 시 WARNING 로깅</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>DebateMode 합의 집계/종료 판정</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>v0.6.4</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>v0.7.0</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>최종 통합문을 self.agents[0] 단독 생성하여 교체된 백업 모델로 편향</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>agents[0](Claude)이 장애로 백업 교체된 상태에서 합의 종료</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>1. Claude 장애 -&gt; 백업 교체
+2. 합의 도달
+3. 통합문 생성이 self.agents[0](교체된 백업) 단독 -&gt; 해당 모델 편향</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>원인: 고정 인덱스 0번 사용. 수정: _select_final_answer_agent()로 교체 안 된 원본 우선 선택, 원본 전멸 시 LLM 없이 결정론적 머지 폴백</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>DebateMode 합의 통합 답변 품질/편향</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>v0.6.4</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>v0.7.0</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>난이도 기반 라운드 라우팅(단순 조기 종료, 복잡 최소 라운드 확보)</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>_classify_difficulty 휴리스틱(길이/코드.기술 키워드/다항/실시간)으로 단순=조기종료 허용, 복잡=COMPLEX_MIN_ROUNDS(3) 전 조기종료 금지. followup은 원주제+질문 합산 분류</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>단순 질문도 고정 다라운드라 토큰/지연 낭비. 3개 AI 교차검증은 유지하면서 비용만 절감(사용자 결정: 라운드 수만 조절)</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>DebateMode.start/followup 라운드 수</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>v0.6.4</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>v0.7.0</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>조건부 반박 강제(challenge-once 반동조 게이트) + disagreements 스키마</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>라운드2+ 프롬프트를 강제 동의/반박에서 "의견 갈리면 상대 주장 구체 인용해 지적, 같으면 같다고(억지 반박 금지)"로 변경. CONSENSUS에 disagreements 필드. 요약 발산(min-pair Jaccard) 시 전원 agree인데 아무도 차이를 안 다루면 1회 교전 라운드 강제 후 미해결 쟁점 명시하고 종료(영구 차단 아님)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>기존 토론이 의견이 갈려도 얼버무리고 동조 수렴. 사용자 피드백: 차이 있을 때 지적 부족. 무한 강제는 비용 증가라 1회 교전으로 한정</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>DebateMode 프롬프트/종료 판정, SYSTEM_PROMPT</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>v0.6.4</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>v0.7.0</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:L94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5792,7 +5792,6 @@
           <t>난이도 기반 라운드 라우팅(단순 조기 종료, 복잡 최소 라운드 확보)</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>_classify_difficulty 휴리스틱(길이/코드.기술 키워드/다항/실시간)으로 단순=조기종료 허용, 복잡=COMPLEX_MIN_ROUNDS(3) 전 조기종료 금지. followup은 원주제+질문 합산 분류</t>
@@ -5848,7 +5847,6 @@
           <t>조건부 반박 강제(challenge-once 반동조 게이트) + disagreements 스키마</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>라운드2+ 프롬프트를 강제 동의/반박에서 "의견 갈리면 상대 주장 구체 인용해 지적, 같으면 같다고(억지 반박 금지)"로 변경. CONSENSUS에 disagreements 필드. 요약 발산(min-pair Jaccard) 시 전원 agree인데 아무도 차이를 안 다루면 1회 교전 라운드 강제 후 미해결 쟁점 명시하고 종료(영구 차단 아님)</t>
@@ -5880,6 +5878,70 @@
         </is>
       </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>실시간/사실 주제에서 같은 권고 반복하며 MAX 라운드까지 토큰 낭비(non-termination)</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>DEBATE 채널, 실시간 시세/사실 질의(예: 오늘 코스피 매수?)</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>1. 실시간/사실 주제 토론 시작
+2. 라운드 3부터 3사 핵심 권고 동일
+3. 인용 수치/출처가 라운드마다 달라 _summaries_diverge가 diverged=True 영구
+4. 곁가지로 agree=false 유지 → agrees&lt;2 → challenge-once/_is_stalemate 미발동
+5. MAX_DEBATE_ROUNDS(10)까지 진행(실측 7R ~)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>원인: _summaries_diverge가 summary 전체(인용 포함) 어휘 Jaccard라 권고 수렴해도 발산 고착, 종료 출구가 agree 플래그에 의존. 수정: agree/cross-agent 발산 무관한 자기-반복 _no_progress(prev,curr) 순수함수(공통 에이전트 자기 summary Jaccard 최소&gt;=0.6) 도입, start/followup 양 루프 prev_summaries 추적 + stalemate elif 다음 elif 추가. min_rounds 이후·정상경로 후순위로 조기 가로채기 방지</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>DebateMode.start/followup 종료 판정, 토론 비용/지연</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>v0.7.0</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>v0.7.1</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
         <is>
           <t>Major</t>
         </is>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5947,6 +5947,61 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Antigravity CLI(agy) 마이그레이션 준비: GEMINI_CLI_BINARY 환경변수 토글</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>GEMINI_CLI_BINARY 환경변수(기본 gemini, 허용 gemini/agy, 그 외는 gemini로 폴백) 도입. agents/gemini.py 에 _build_subprocess_args 헬퍼 추가: gemini=['gemini','-m',model,'-y','-p',''] + stdin pipe / agy=['agy','--dangerously-skip-permissions','-p',prompt] + stdin DEVNULL. _available_models()는 agy일 때 placeholder만 반환, _mark_failed()는 no-op. _run_cli/_run_progress_once 가 헬퍼+조건부 DEVNULL 사용. 기본값 gemini 유지로 즉시 배포해도 기존 동작 100% 보존</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2026-05-19 Google I/O 2026에서 Gemini CLI 종료 + Antigravity CLI 통합 공식 발표(Google Developers Blog). 2026-06-18부터 Google AI Pro/Ultra/무료 사용자 Gemini CLI 요청 차단. 사전에 코드 경로를 분기 가능하도록 준비해 D-day 직전 긴급 배포 위험 회피, 6/18까지 dry-run/실측 시간 확보</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>agents/gemini.py, config.py, tests/test_gemini.py 및 토론/코딩/브릿지 모드의 Gemini 호출 경로 (런타임 동작은 환경변수 미설정 시 기존과 동일)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>v0.7.1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>v0.7.2</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L95"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6002,6 +6002,68 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>agy 호출이 cmd /c 로 감싸져 prompt 메타문자가 셸 파싱됨 + argv 길이 한계 미가드</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>GEMINI_CLI_BINARY=agy 환경에서만 발현. 기본값 gemini 사용 시 영향 없음</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>1. GEMINI_CLI_BINARY=agy 토글
+2. Slack 에 prompt 가 &amp; | ^ % &lt; &gt; 같은 메타문자 포함 메시지 전송 (예: "검색: foo &amp; bar | grep")
+3. cmd.exe 가 &amp; 를 명령 구분자로 해석해 agy 인자가 깨짐 / 또는 코딩 모드에서 Claude 응답+코드가 길어져 32KB CommandLine 한계 초과 시 CreateProcess 실패</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>원인: process.py 의 platform_cmd 가 모든 명령을 cmd /c 로 감싸서 native .exe 인 agy 도 셸 파싱 거치고, agy 의 prompt 는 argv 직접 전달이라 32KB 한계 영향. 수정: (1) process.py 에 _NATIVE_EXE_NAMES 화이트리스트 + _resolve_native_exe 헬퍼 추가, agy 는 cmd /c 우회하고 절대경로로 직접 실행. (2) agents/gemini.py 에 _AGY_PROMPT_ARGV_LIMIT=25000 + _truncate_for_agy_argv 헬퍼 추가, 초과 시 머리만 사용 + [...truncated] 표식. (3) _build_cmd 가 agy 경로 빈 prompt 에 ValueError raise. (4) 테스트 absent env vs empty value 분리 + 미사용 변수 제거</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>agents/gemini.py, process.py, tests/test_process.py, tests/test_gemini.py (Windows agy 경로만 영향. gemini 경로 동작 불변)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>v0.7.2</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>v0.7.2.1</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:L97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6064,6 +6064,69 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2-vs-1 deadlock 토론이 MAX 라운드까지 끌림 (agrees&lt;2 라 _is_stalemate 미발동)</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>3 에이전트 중 1명이 출처 없이 이견 지속 + 나머지 2명이 (서로 합의했음에도) agree=false 마킹</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>1. DEBATE 채널에서 "런던고라니 옛날 정치-경제 분리 발언 찾을 수 있나" 등 출처 추적이 안되는 질문
+2. R1~R5 진행: Claude+Codex 가 "출처 URL 없는 인용은 환각 위험" 입장 합의, Gemini 가 매 R 마다 약간 다른 인용 변형 제시
+3. 기존 종료 조건: agrees&gt;=3(전원 합의) 또는 agrees&gt;=2 + _is_stalemate(2R 발산 지속). 모두 agrees 카운트가 발목
+4. 결국 no_progress(전원 자기 반복 Jaccard&gt;=0.6) 가 R5 에 가까스로 발동 또는 MAX_DEBATE_ROUNDS(10) 도달</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>원인: (1) SYSTEM_PROMPT 의 agree=true 정의가 전원 일치 묵시("다른 에이전트들과 의견이 충분히 일치")라 Claude/Codex 가 Gemini 와 일치 안 하니 agree=false 마킹. (2) 페어 합의 + outlier 패턴을 명시 감지하는 로직 없음. 수정: (A) SYSTEM_PROMPT 완화 "최소 1명의 다른 에이전트와 충분히 일치". (B) _pair_outlier 헬퍼 신설(페어와이즈 Jaccard, best&gt;=0.30 + outlier 페어들 &lt;=60%면 outlier 이름 반환), _persistent_outlier 헬퍼(같은 outlier 2R 연속이면 종료 신호), start/followup 양 루프에 "다수 합의 (2/3, {outlier} 이견 지속)" 분기 추가. agree 카운트 무관하게 안전망</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>DebateMode start/followup 종료 로직, 모든 토론 채널의 비용/속도 (페어 outlier 케이스에서 R3 종료)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>v0.7.2.1</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>v0.7.3</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6127,6 +6127,69 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Gemini Semaphore 이벤트 루프 바인딩 회귀로 토론 33분 hang + 응답 손실</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Slack Bolt 가 토론마다 새 이벤트 루프 컨텍스트에서 핸들러 호출</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>1. 봇 재시작 후 슬랙 채널에 토론 발신
+2. 첫 토론 R1 또는 R2 에서 Gemini 응답 손실 ("Semaphore object at 0x... is bound to a different event loop" 에러 또는 작업 중 N초 표시 후 무응답)
+3. 백업 Claude-B 정상 투입되어 토론은 진행되나 1라운드 Gemini 데이터 손실
+4. 일부 케이스(thread 1779275130 등산vs헬스): Semaphore acquire 단계 hang → _run_progress_once 의 overall_timeout(t*2=360s) 검사가 while loop 안에 있어 진입 못 함 → 33분(2019초) 진행 표시만 계속, 종료 메시지 없이 영구 멈춤</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>원인: (1) 모듈 전역 _gemini_concurrency = asyncio.Semaphore(3) 가 첫 사용 이벤트 루프에 바인딩되는 Python asyncio 한계. Slack Bolt 의 새 이벤트 루프에서 acquire 시 "bound to different loop" 에러. (2) Semaphore acquire 단계에서 block 되면 _run_progress_once 의 while True 내부 overall_timeout 검사가 발동 못 함. 수정: (A) WeakKeyDictionary 기반 per-loop lazy init 으로 _get_gemini_concurrency() 헬퍼 신설, 호출 사이트 2개 갱신. (B) ask_with_progress 의 _run_progress_once 호출을 asyncio.wait_for(timeout=t*2.5) 외부 가드로 래핑, 내부 timeout 우회되어도 강제 cancel + 프로세스 정리. 신규 단위 5건 추가, 전체 250 passed</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>agents/gemini.py 의 모든 Gemini 호출 경로 (토론/코딩/브릿지 모드 전부)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>v0.7.3</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>v0.7.3.2</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L98"/>
+  <dimension ref="A1:L99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6190,6 +6190,69 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>v0.7.3.2 핫픽스 누락: _run_progress_once L293 _gemini_concurrency 잔존 + cancel cleanup 부재</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>v0.7.3.2 배포 후 봇 재시작 직후</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1. v0.7.3.2 봇 재시작
+2. 첫 Gemini 호출(ask_with_progress 경로) 시 _run_progress_once L293 에서 NameError: _gemini_concurrency 미정의
+3. 모든 토론/코딩 모드 Gemini 진행성 호출 즉시 실패
+4. 추가: 외부 wait_for cancel 발생 시 spawn 직후~register 이전 cancel window 에 좀비 프로세스 leak</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>원인: v0.7.3.2 의 replace_all=true 가 들여쓰기 차이로 _run_cli L220 만 잡고 _run_progress_once L275(현 L293) 는 놓침. Codex 교차검증 (1) Block 발견. 추가: 두 함수 모두 subprocess lifecycle 에 try/finally cleanup 없어 외부 cancel 시 좀비. 수정: (A) L293 _gemini_concurrency → _get_gemini_concurrency() 교체. (B) _run_cli proc.communicate 호출을 try/except BaseException 으로 감싸 cancel 시 kill_process_tree + 짧은 wait. (C) _run_progress_once 의 spawn 이후 전체 lifecycle 을 try/finally 로 감싸고 finally 에 proc.returncode is None 검사 후 kill_process_tree + wait_for(2s). 전체 비-라이브 250 passed 회귀 없음</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>agents/gemini.py 의 모든 Gemini 호출 경로 (NameError 로 진행성 호출 100% 실패)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>v0.7.3.2</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>v0.7.3.3</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6253,6 +6253,62 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>PDF 첨부 지원 추가 (이미지에 더해 PDF 도 각 CLI read 도구로 처리) + images → attachments 전체 리네이밍</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>slack_files.extract_images 가 image/* MIME 만 다운로드, PDF 던지면 봇이 무시. application/pdf 추가 + kind 필드 + size 분기 (이미지 5MB / PDF 20MB). 각 에이전트 prompt augment 함수가 kind 분기된 안내 생성 (Claude Read native PDF / Gemini @path / Codex read 텍스트 추출). Python pymupdf 등 PDF 파싱 의존성 추가 없음 (글로벌 CPU 과열 룰 정합). 부수: extract_images → extract_attachments, _augment_with_image_paths/note → _augment_with_attachments, images 인자/변수 → attachments 전체 통일, BridgeMode._call_claude_vision → _call_claude_with_attachments.</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>사용자가 KB 보험제안서 PDF 같은 일반 문서를 슬랙 봇에 던지면 분석/요약 받기를 원하는데, 기존 이미지 전용 흐름이라 PDF 가 무시되던 문제. 모든 CLI 의 read 도구가 PDF 를 native 처리하므로 MIME 필터만 풀어주면 거의 자동 동작. 변수명/함수명도 의미상 attachments 가 정확.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>slack_files.py + 각 에이전트 (claude/codex/gemini) + backup 3 + modes/{bridge,coding,debate} + slack_bot.py + 테스트 5건. 슬랙 PDF 첨부 흐름 전반.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>v0.7.3.3</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>v0.7.4</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L100"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6272,7 +6272,6 @@
           <t>PDF 첨부 지원 추가 (이미지에 더해 PDF 도 각 CLI read 도구로 처리) + images → attachments 전체 리네이밍</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>slack_files.extract_images 가 image/* MIME 만 다운로드, PDF 던지면 봇이 무시. application/pdf 추가 + kind 필드 + size 분기 (이미지 5MB / PDF 20MB). 각 에이전트 prompt augment 함수가 kind 분기된 안내 생성 (Claude Read native PDF / Gemini @path / Codex read 텍스트 추출). Python pymupdf 등 PDF 파싱 의존성 추가 없음 (글로벌 CPU 과열 룰 정합). 부수: extract_images → extract_attachments, _augment_with_image_paths/note → _augment_with_attachments, images 인자/변수 → attachments 전체 통일, BridgeMode._call_claude_vision → _call_claude_with_attachments.</t>
@@ -6306,6 +6305,69 @@
       <c r="L100" t="inlineStr">
         <is>
           <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>v0.7.4 PDF 첨부 실전 회귀: Gemini workspace 격리 + Codex read 도구 PDF 미지원</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>v0.7.4 배포 직후 실제 슬랙 스레드(1779791375.628899) 에서 PDF 첨부 테스트</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>1. Slack #ai-debate 채널에 PDF 첨부 + 평가 요청 메시지
+2. Gemini: Error executing tool read_file: Path not in workspace 에러로 PDF 자체 못 읽음
+3. Codex: pdftotext 미설치 → pypdf import 시도 → 일부 페이지만 추출 후 부분 답변
+4. Claude 만 정상 분석 완료</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>원인: (1) Gemini CLI 의 read_file 도구가 임시 디렉토리(AppData/Local/Temp/slack_attachments_*) 를 workspace 외부로 판단하고 거부. (2) Codex CLI 의 read 도구가 PDF native 미지원. 수정: (A) slack_bot.py 의 tmp_dir 을 &lt;project&gt;/.tmp/ 내부로 변경 (Gemini workspace 회피). (B) slack_files.py 에 extract_pdf_text + format_pdf_text_inline 헬퍼 추가, PDF 다운로드 직후 pypdf 로 텍스트 추출 → 반환 dict 의 text 필드. (C) 각 에이전트 _augment_with_attachments 가 PDF text 를 prompt 에 인라인 블록으로 첨부. Codex instruction 에 pdftotext 시도 금지 명시. (D) requirements.txt 에 pypdf&gt;=4.0 추가. (E) .gitignore 에 .tmp/ 추가.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>slack_bot.py + slack_files.py + agents/{claude,codex,gemini}.py + 테스트 2건. 슬랙 PDF 첨부 시 Gemini/Codex 모두 실패하던 흐름 복구.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>v0.7.4</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>v0.7.5</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Major</t>
         </is>
       </c>
     </row>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6371,6 +6371,69 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>v0.7.5 자체 회귀: slack_bot.py 의 os import 누락으로 PDF/이미지 첨부 시 _runner NameError 무응답</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>v0.7.5 (a37ae5f) 배포 직후 실전 PDF 첨부 테스트 (슬랙 스레드 1779797934.173099)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>1. v0.7.5 봇 재시작 후 슬랙 채널에 PDF 첨부 + 평가 요청 메시지
+2. 봇 완전 무응답 (Round 1/2/3 진행 표시조차 없음)
+3. bot_output.log 확인: Exception in thread Thread-10 (_runner): NameError: name 'os' is not defined (slack_bot.py:173)
+4. 첨부 없는 일반 텍스트 메시지는 정상 동작 (라우팅이 _runner 진입 전 분기)</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>원인: v0.7.5 에서 tmp_dir 을 &lt;project&gt;/.tmp/ 내부로 옮길 때 _runner 안에서 os.path.join / os.makedirs 를 추가했는데 모듈 전역에 import os 가 없음. 함수 내부 import tempfile, shutil 만 추가하고 os 는 빠뜨림. 수정: (A) slack_bot.py 모듈 전역 import 에 os 추가. (B) tests/test_slack_bot.py 에 test_os_module_imported 회귀 테스트 추가 (모듈에 os attribute 존재 + 진짜 os 모듈인지 검증).</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>slack_bot.py + tests/test_slack_bot.py. v0.7.5 commit 부터 v0.7.6 fix 까지 약 30분간 모든 첨부 메시지 봇 무응답.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>v0.7.5</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>v0.7.6</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:L103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6434,6 +6434,68 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>토론 합의된 답변이 모델 답변 대신 'API Error: 500 Internal server error' 에러 문구로 방송됨</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>통합문 생성 에이전트(원본 Claude)가 합의문 생성 시점에 Anthropic API 5xx(500/529 등)를 맞는 경우 (슬랙 스레드 1780056574.625539)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>1. stockradar 채널에 사실형 질문 토론 요청 (예: '1990년부터 삼성전자 시총 코스피 비중')
+2. 라운드 1~3 정상 진행, 전원 요약까지 정상
+3. 마지막 '💡 합의된 답변:' 자리에 'API Error: 500 Internal server error. This is a server-side issue...' 가 그대로 출력됨</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>원인: 합의문은 _generate_final_answer() 가 agent.ask() 로 생성. Claude Code CLI 는 API 5xx 시 예외를 던지지 않고 --output-format json 의 result 필드에 'API Error: 500 ...' 문구를 담아 정상 종료 → (1) agents/base.py _is_fatal_error 가 429/quota 만 알고 5xx/overloaded 패턴이 없어 has_error=False, (2) _generate_final_answer 의 try/except 는 파이썬 예외만 잡아 문자열 에러를 통과시켜 그대로 broadcast. 수정: (A) agents/base.py _FATAL_SUBSTRINGS 에 'internal server error','overloaded_error' 추가 + _FATAL_REGEX 에 5xx alternative (error|status|code 앵커 뒤 5xx, API Error/APIError/statusCode/HTTP/1.1 포맷 포함, 500자/약 500조/목표가 529,000원/handler.py:500 오탐 없음). (B) modes/debate.py _generate_final_answer 를 후보 순회+1회 재시도+_is_bad_final_answer 검사+_deterministic_merge 폴백으로 재작성하여 에러 문자열이 절대 합의문으로 방송되지 않도록 함. 회귀 테스트 추가(test_agent_base.py, test_consensus.py). Codex 교차검증 후 268 passed.</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>modes/debate.py 토론 종료 합의문 + agents/base.py fatal error 감지(라운드 중 5xx 백업 교체 포함). 사용자에게 에러 문구가 최종 답변으로 노출됨.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>v0.7.6</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>v0.7.7</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L103"/>
+  <dimension ref="A1:L104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6496,6 +6496,67 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Gemini 매 발언 첫 줄에 'True color (24-bit) support not detected' 터미널 경고 누출</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>non-TTY 환경에서 Gemini CLI 호출 시 (자체 테스트 thread 1780059304.126349)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>1. stockradar 채널에서 토론 실행
+2. Gemini 발언마다 첫 줄에 'Warning: True color (24-bit) support not detected. Using a terminal with true color enabled will result in a better visual experience.' 가 본문 앞에 노출됨</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>원인: agents/gemini.py 의 _clean_output 노이즈 필터가 _NOISE_KEYWORDS 의 키워드 포함 라인을 제거하는데, 색상 경고로 '256-color support not detected' 만 등록돼 있어 실제 출력되는 'True color (24-bit) support not detected' 변종이 필터를 통과해 응답에 섞임. 수정: _NOISE_KEYWORDS 의 '256-color support not detected' 를 공통 꼬리 'support not detected' 로 교체하여 256-color/True color(24-bit) 및 향후 변종을 모두 필터. tests/test_gemini.py::TestCleanOutput 에 true-color 케이스 회귀 테스트 추가. 단위 269 passed, 실제 Gemini 호출 + 슬랙 전수 스캔 확인, Codex 교차검증 통과. 추가: 자체 테스트가 합의문만 검사해 이 노이즈를 놓쳤던 문제도 전수 스캔 방식으로 개선.</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Gemini 에이전트 Slack 답변 외관. 기능 오류는 아니나 매 발언에 경고 노이즈 노출.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>v0.7.7</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>v0.7.8</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L104"/>
+  <dimension ref="A1:L105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6557,6 +6557,68 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>토론 결론의 "미해결 쟁점"이 각 에이전트 요약/합의된 답변과 중복 (disagreements 필드 미사용 dead data)</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>토론이 발산(diverged) 상태로 종료될 때</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>1. 토론 채널에 의견이 갈릴 주제 입력
+2. 결론 메시지에서 "📋 각 에이전트 요약"과 "⚠️ 미해결 쟁점"이 같은 summary 를 나열
+3. "💡 합의된 답변"과도 유사한 내용이 반복 노출됨</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>원인: CONSENSUS JSON 에 실제 대립점용 disagreements([{agent,point,why}]) 전용 필드가 있고 시스템 프롬프트가 채우라 지시하나, 코드가 한 번도 읽지 않는 dead data 였음. _summaries_diverge() 가 issue_note 를 disagreements 가 아니라 각 에이전트 summary[:120] 로 생성 → 결론의 "각 에이전트 요약"(summary 전체) 및 "합의된 답변"과 중복. 다음 라운드 프롬프트 주입에도 같은 노트가 쓰여 수렴 유도 약화. 수정: _format_issue_note() 헬퍼 신설로 disagreements 의 point/why 만으로 노트 생성("{name}: {point} ({why})"), 구조적 대립점이 없으면 빈 문자열 반환해 "미해결 쟁점" 줄 자체 생략(표시+주입 3곳 모두 if issue_note 가드). 발산 감지(Jaccard)·교전강제 로직은 불변. 단위 테스트 294 passed + 슬랙 E2E 3종 중복 0건 + Codex 정적 교차검증 통과.</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>modes/debate.py 토론 결론 메시지 표시 + 다음 라운드 프롬프트 주입</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>v0.7.8</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>v0.7.9</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L105"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6619,6 +6619,62 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>agy `-p` stdout 미출력 버그(#76) 우회 - 디스크 transcript 에서 trace 토큰으로 응답 복구</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>agy(Antigravity CLI) 백엔드(GEMINI_CLI_BINARY=agy)에서 `-p`가 non-TTY 에 stdout 응답을 안 쓰는 upstream 버그(#76)를 우회. 호출별 고유 trace 토큰(AGYTRACE+uuid)을 prompt 끝에 심고(argv 절단 이후 append 로 유실 방지), 디스크 transcript (brain/&lt;cid&gt;/.system_generated/logs/transcript.jsonl)의 USER_INPUT 에서 그 토큰이 박힌 턴의 최종 PLANNER_RESPONSE 만 회수. _recover_agy_response/_extract_traced_response/_iter_turns/_trace_in 신설, _run_cli·_run_progress_once 통합. cwd→cid 매핑 1차 + since_ts 이후 transcript 스캔 2차(둘 다 토큰 매칭). cid UUID 검증·content 정규화·마커 strip 포함.</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Gemini CLI 개인 티어가 2026-06-18 종료 예정인데, 후계 agy 는 #76(2026-06-09 OPEN, 1.0.6 미수정)으로 비대화형 stdout 이 비어 봇 백엔드로 못 썼다. 응답이 디스크엔 정상 저장되는 점을 이용해 복구 경로를 붙여 agy 를 실사용 가능 상태로 준비. trace 토큰 방식이라 동시 호출/대화 재사용/공통 prompt prefix 에도 다른 호출 응답을 오회수하지 않음. Codex 3차 교차검증 통과 + 라이브 실측 3회(stdin=DEVNULL 에서 agy 1.0.6 EXIT=0/STDOUT_LEN=0 인데 토큰 복구로 정확 회수).</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>agents/gemini.py (GEMINI_CLI_BINARY=agy 경로). gemini 기본 경로는 토큰 무시로 무영향.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>v0.7.9</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>v0.7.10</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L106"/>
+  <dimension ref="A1:L107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6638,7 +6638,6 @@
           <t>agy `-p` stdout 미출력 버그(#76) 우회 - 디스크 transcript 에서 trace 토큰으로 응답 복구</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>agy(Antigravity CLI) 백엔드(GEMINI_CLI_BINARY=agy)에서 `-p`가 non-TTY 에 stdout 응답을 안 쓰는 upstream 버그(#76)를 우회. 호출별 고유 trace 토큰(AGYTRACE+uuid)을 prompt 끝에 심고(argv 절단 이후 append 로 유실 방지), 디스크 transcript (brain/&lt;cid&gt;/.system_generated/logs/transcript.jsonl)의 USER_INPUT 에서 그 토큰이 박힌 턴의 최종 PLANNER_RESPONSE 만 회수. _recover_agy_response/_extract_traced_response/_iter_turns/_trace_in 신설, _run_cli·_run_progress_once 통합. cwd→cid 매핑 1차 + since_ts 이후 transcript 스캔 2차(둘 다 토큰 매칭). cid UUID 검증·content 정규화·마커 strip 포함.</t>
@@ -6672,6 +6671,66 @@
       <c r="L106" t="inlineStr">
         <is>
           <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Windows 슬랙 문의 시 cmd 콘솔 창 깜빡임 (claude 호출의 전역 MCP context7 spawn)</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>사용자 전역 Claude 설정에 stdio 방식 MCP(context7 = npx -y @upstash/context7-mcp) 등록 + Windows 환경</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>슬랙에서 봇에 문의 → 에이전트 '생각 중' 진입 시점에 cmd/conhost 콘솔 창이 잠깐 떴다 사라짐. claude 에이전트가 호출될 때마다 재현(가끔처럼 보이나 claude 경로면 상시).</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>원인: 봇이 `cmd /c claude -p ...` 로 Claude Code CLI 호출 시, claude 가 부팅하며 전역 MCP context7 을 `cmd /c npx ...` 로 새로 spawn. claude.exe 가 CREATE_NO_WINDOW(숨김 콘솔)로 떠 있어 이 손자 프로세스가 부모 숨김 콘솔을 못 물려받고 새 conhost 콘솔을 할당 → 깜빡임. 수정: claude 호출부(agents/claude.py _build_cmd/_build_stream_cmd, modes/bridge.py _call_claude)에 `--strict-mcp-config` 추가 → 전역 MCP 0개 로드(context7 spawn 제거). 라이브 격리 비교(있음 spawn=False / 없음 spawn=True) + Codex 교차검증 통과.</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>agents/claude.py, modes/bridge.py. Windows 에서 claude 에이전트가 타는 모든 경로(토론/브릿지/첨부 분석). codex(MCP url= HTTP 원격)·gemini 무관.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>v0.7.10</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>v0.7.11</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Minor</t>
         </is>
       </c>
     </row>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L107"/>
+  <dimension ref="A1:L108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6734,6 +6734,62 @@
         </is>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>리서치 모드 신설 (#ai-리서치, 3 AI 분담형 팬아웃 조사+교차검증+출처 리포트)</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>#ai-리서치 채널 질문 → 분해(claude, 하위질문 JSON) → 하위질문 라운드로빈 분담 조사(claude/codex/gemini 병렬, 웹) → 생산자!=검증자 교차검증(supported/disputed/unverified) → claude 종합 → Slack 스레드 전송. modes/research.py 신설(순수 엔진 함수 + ResearchMode), config(RESEARCH_CHANNEL_ID/RESEARCH_SUBQ_MAX)·slack_bot 라우팅. 견고성: 분해 실패 단일질문 degrade, asyncio.gather(return_exceptions=True), _ask_named 백업 인계, disputed/unverified 드롭 없이 리포트 표기.</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>기능 확장 방향으로 토론 고도화+리서치를 원했고 둘이 같은 '근거 기반 협업 코어'(웹 근거·상호 교차검증·출처)를 공유 → 엔진 한 번 구현해 두 모드로 노출(Phase 1=리서치, Phase 2=토론 고도화). 실사용 가치(출처 달린 신뢰 리포트) + 토론 고도화 토대 확보.</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>modes/research.py(신규), config.py, slack_bot.py, README/.env.example. 신규 #ai-리서치 채널. 기존 토론/코딩/브릿지 모드 무영향.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>v0.7.11</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>v0.8.0</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L108"/>
+  <dimension ref="A1:L110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6753,7 +6753,6 @@
           <t>리서치 모드 신설 (#ai-리서치, 3 AI 분담형 팬아웃 조사+교차검증+출처 리포트)</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>#ai-리서치 채널 질문 → 분해(claude, 하위질문 JSON) → 하위질문 라운드로빈 분담 조사(claude/codex/gemini 병렬, 웹) → 생산자!=검증자 교차검증(supported/disputed/unverified) → claude 종합 → Slack 스레드 전송. modes/research.py 신설(순수 엔진 함수 + ResearchMode), config(RESEARCH_CHANNEL_ID/RESEARCH_SUBQ_MAX)·slack_bot 라우팅. 견고성: 분해 실패 단일질문 degrade, asyncio.gather(return_exceptions=True), _ask_named 백업 인계, disputed/unverified 드롭 없이 리포트 표기.</t>
@@ -6787,6 +6786,128 @@
       <c r="L108" t="inlineStr">
         <is>
           <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>리서치 최종 종합 답변이 채널에 안 보이고 스레드에만 남음</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>리서치 모드(#ai-리서치) 사용 + 결과를 채널 타임라인에서 확인하려는 경우</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>1. #ai-리서치 에 질문 전송
+2. 리서치 완료 후 종합 답변이 스레드 안에만 게시되고 채널 타임라인엔 표시 안 됨</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>원인: ResearchMode 가 종합 답변/리포트를 _post_long(스레드 전용)으로만 전송. 수정: debate 처럼 _broadcast_long(첫 청크 reply_broadcast=True)로 종합 답변을 채널에도 노출, 상세 출처/쟁점 리포트는 스레드 유지. 회귀 테스트 추가(26건), 라이브 확인.</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>modes/research.py (리서치 모드 결과 전송)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>v0.8.0</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>v0.8.1</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Windows에서 봇 작업 시 cmd 콘솔 창 깜빡임 (agy statusline)</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>GEMINI_CLI_BINARY=agy + agy 전역 설정 statusLine.enabled=true + Windows</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>1. 봇이 agy 호출하는 작업(리서치/토론) 실행
+2. 진행 중 cmd/sh 콘솔 창이 주기적으로 떴다 사라짐</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>원인: agy 가 statusLine 명령을 주기적으로 셸(cmd /c·sh -c)로 실행 → 그 셸 콘솔이 깜빡임. 세션 격리(S4U)는 상시 로그인 시 같은 세션이라 무효, statusLine 명령 변경도 agy 가 항상 셸 래핑이라 무효. 최종: agy 전역 설정 statusLine.enabled=false 로 비활성(사용자 선택). 부수로 봇을 S4U 비대화형 예약작업으로 전환(로그아웃 복원력) + watchdog DETACHED/BREAKAWAY 기동 + CREATE_NO_WINDOW 보강. 격리 실측으로 새 agy statusline 0건 확인. (v0.7.11 claude context7 와 별개 원인)</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>watchdog_guard.py, watchdog.py, migrate_session0.ps1, agy 전역 settings.json(레포 외). agy 쓰는 전 모드(토론/코딩/리서치)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>v0.7.11</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>v0.8.1</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Minor</t>
         </is>
       </c>
     </row>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L110"/>
+  <dimension ref="A1:L112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6911,6 +6911,123 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>agy 자동 업데이트 비활성화로 봇 가동 중 안정성 확보</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>GEMINI_CLI_BINARY=agy 일 때 config.make_filtered_env() 가 자식 프로세스 env 에 AGY_CLI_DISABLE_AUTO_UPDATE=1 을 주입</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>agy 는 호출 시 백그라운드 업데이터로 자기 실행 파일을 자동 교체(update_status.json 에 "Update successful, restart CLI to use" 실제 이력). 봇 가동 중 교체되면 진행 중 호출이 깨질 수 있어 자동 업데이트를 차단(버전 고정·안정성). 깜빡임 방지가 아니라 안정성 목적.</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>agy 사용 시 모든 에이전트 호출(config.make_filtered_env)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>v0.8.1</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>v0.8.2</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>리서치 모드에서 agy 자동 업데이터(agy --version) 콘솔 창 깜빡임</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>GEMINI_CLI_BINARY=agy + 봇이 대화형 세션(로그인 상태)에서 가동</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>1. #ai-리서치 채널에 질문 전송
+2. agy 가 병렬 호출될 때마다 cmd 콘솔 창이 잠깐 떴다가 사라짐(깜빡임)</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>원인: agy 가 호출마다 백그라운드 업데이터(agy --bg-updater → agy --version)를 띄우고, 그 버전체크 콘솔 창이 대화형 데스크톱에 수십 ms 노출됨(봇이 못 막는 detached 손자). 리서치는 agy 6+개 병렬 호출이라 두드러짐. 억제 시도 전부 실측 무효: AGY_CLI_DISABLE_AUTO_UPDATE(버전체크 창 잔존)/last_check 미래화/S4U 세션격리(로그인 중 동일 세션)/부모 CREATE_NO_WINDOW/숨김 데스크톱 lpDesktop/agy CLI 플래그(없음). 처분: 알려진 agy 한계로 수용·문서화(기능 영향 없음). v0.7.11 claude context7, v0.8.1 agy statusline 과는 별개 제3원인.</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>agy 사용 시 모든 에이전트 호출(리서치 모드 병렬에서 부각), Windows 대화형 세션</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>v0.8.0</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>v0.8.2(수용)</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Trivial</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L112"/>
+  <dimension ref="A1:L113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6930,7 +6930,6 @@
           <t>agy 자동 업데이트 비활성화로 봇 가동 중 안정성 확보</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>GEMINI_CLI_BINARY=agy 일 때 config.make_filtered_env() 가 자식 프로세스 env 에 AGY_CLI_DISABLE_AUTO_UPDATE=1 을 주입</t>
@@ -7025,6 +7024,62 @@
       <c r="L112" t="inlineStr">
         <is>
           <t>Trivial</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>리서치 리포트 출처를 Slack 하이퍼링크로 축약(긴 URL 숨김)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>출처 블록을 "도메인: 전체URL" → Slack "&lt;url|짧은라벨&gt;" 형식으로 변경. 라벨=도메인+짧고 의미있는 경로 끝(percent-encoding 디코딩), 경로 없음/28자초과/무의미하면 도메인만. 신규 _short_source_label() (modes/research.py).</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>#ai-리서치 실사용 스레드에서 출처 URL이 너무 길게 표시됨(특히 Gemini 웹 그라운딩 redirect 토큰 200자+). 긴 URL을 링크 뒤로 숨겨 가독성 개선, 같은 도메인 다중 출처는 경로 끝으로 구분.</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>리서치 모드 출처 표시(modes/research.py _format_report)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>v0.8.2</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>v0.8.3</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Minor</t>
         </is>
       </c>
     </row>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L113"/>
+  <dimension ref="A1:L114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7046,7 +7046,6 @@
           <t>리서치 리포트 출처를 Slack 하이퍼링크로 축약(긴 URL 숨김)</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>출처 블록을 "도메인: 전체URL" → Slack "&lt;url|짧은라벨&gt;" 형식으로 변경. 라벨=도메인+짧고 의미있는 경로 끝(percent-encoding 디코딩), 경로 없음/28자초과/무의미하면 도메인만. 신규 _short_source_label() (modes/research.py).</t>
@@ -7078,6 +7077,62 @@
         </is>
       </c>
       <c r="L113" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>리서치 종합 답변 본문의 인라인 URL도 짧은 하이퍼링크로 축약</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>v0.8.3(출처 블록 축약) 후속. 모델 생성 본문(종합 답변 synth + finding 텍스트)의 URL을 _shorten_urls_in_text() 로 정규화: 마크다운 [label](&lt;url&gt;)/[label](url), 꺾쇠 &lt;url&gt;/&lt;url|label&gt;, raw URL 3단계 치환 → Slack &lt;url|짧은라벨&gt;. trailing 문장부호 절단, lookbehind 로 이중치환 방지, 멱등성 보장.</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>v0.8.3 배포 후 라이브 확인 시 구조화 출처 블록은 축약됐으나 모델이 [매체명](&lt;url&gt;) 마크다운으로 박은 인라인 출처가 Slack 마크다운 링크 미지원으로 URL 원문 노출(특히 Gemini 그라운딩 redirect 200자+). 본문도 축약해 가독성 확보.</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>리서치 모드 종합 답변/리포트 본문 표시(modes/research.py _format_report, ResearchMode.start)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>v0.8.3</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>v0.8.4</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L114"/>
+  <dimension ref="A1:L116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7101,7 +7101,6 @@
           <t>리서치 종합 답변 본문의 인라인 URL도 짧은 하이퍼링크로 축약</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>v0.8.3(출처 블록 축약) 후속. 모델 생성 본문(종합 답변 synth + finding 텍스트)의 URL을 _shorten_urls_in_text() 로 정규화: 마크다운 [label](&lt;url&gt;)/[label](url), 꺾쇠 &lt;url&gt;/&lt;url|label&gt;, raw URL 3단계 치환 → Slack &lt;url|짧은라벨&gt;. trailing 문장부호 절단, lookbehind 로 이중치환 방지, 멱등성 보장.</t>
@@ -7133,6 +7132,118 @@
         </is>
       </c>
       <c r="L114" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>리서치 하위 주제 수 6→4 축소로 응답시간 단축</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>RESEARCH_SUBQ_MAX 기본값 6→4 (config.py 기본값 + .env + .env.example 동기화).</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>리서치 1건에 약 7분 소요. 질문당 AI 호출이 13회(분해1+조사6+검증6+종합1)→10회(조사4+검증4)로 줄어 체감 시간 단축. 커버리지와 속도의 균형점으로 4 선택.</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>리서치 모드 전체 소요시간(config.RESEARCH_SUBQ_MAX)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>v0.8.4</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>v0.8.5</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>리서치 분담조사/교차검증 단계 진행 카운터 (n/N)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>분담 조사·교차검증 단계의 정적 "...중" 메시지를 (0/N) 으로 게시 후 각 병렬 작업 완료 시 chat_update 로 (n/N) 실시간 갱신. 신규 _post_get_ts()/_update() 헬퍼. ts None 시 graceful 무시.</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>리서치가 6~7분 걸리는데 진행 단계가 불투명해 "멈춘 건가?" 답답함(실사용 피드백). 진행률을 눈으로 확인 가능하게 해 멈춤 오인 방지.</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>리서치 모드 진행 메시지(ResearchMode.start)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>v0.8.4</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>v0.8.5</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L116"/>
+  <dimension ref="A1:L118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7156,7 +7156,6 @@
           <t>리서치 하위 주제 수 6→4 축소로 응답시간 단축</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>RESEARCH_SUBQ_MAX 기본값 6→4 (config.py 기본값 + .env + .env.example 동기화).</t>
@@ -7212,7 +7211,6 @@
           <t>리서치 분담조사/교차검증 단계 진행 카운터 (n/N)</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>분담 조사·교차검증 단계의 정적 "...중" 메시지를 (0/N) 으로 게시 후 각 병렬 작업 완료 시 chat_update 로 (n/N) 실시간 갱신. 신규 _post_get_ts()/_update() 헬퍼. ts None 시 graceful 무시.</t>
@@ -7246,6 +7244,122 @@
       <c r="L116" t="inlineStr">
         <is>
           <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>리서치 모드, 교차검증이 찾은 교정 사실 무시 + 긴 링크 분할로 출력 깨짐</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>시점이 중요한 사실형 질문(이벤트/혜택 등)을 #ai-리서치에 투입</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>1. #ai-리서치에 '중개형 ISA 이벤트 증권사 추천' 질문 2. 종합 답변이 '키움뿐'으로 단정(실제 한국투자증권도 6월 진행 중) 3. 이어지는 리서치 리포트의 긴 Gemini 그라운딩 URL이 메시지 경계에서 두 동강나 깨짐</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>원인1: _findings_block이 검증자 NOTE(교정 사실)를 종합 프롬프트에 안 넘겨 유실 → NOTE 포함. 원인2: _post_long/_broadcast_long 맹목 분할이 &lt;url|label&gt; 링크를 절단 → 신규 _split_for_slack 로 줄/링크 경계 보존(초과 링크는 통째로). 원인3: 이중꺾쇠(&lt;&lt;&gt;&gt;) 잔재 → 연속 꺾쇠 축약. + 종합 프롬프트에 dispute 결론 교정/철회 규칙 추가.</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>리서치 모드(ResearchMode) 종합 답변/리포트 정확도·렌더링</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>v0.8.5</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>v0.8.6</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>리서치 모드 1차 출처 정독 + 결론 정교화 재설계</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>조사 단계 1차 출처(공식·공시·규제기관) 직접 fetch·정독 + 최신성(현재 진행중/과거 종료) 구분 의무화. 종합 단계 증거 게이트(1차 1개 포함 출처≥2일 때만 '확정')·진행중/종료/불확실 3구간 분리·비교형 순위표. 검증 단계 인용된 1차 출처 재fetch 로 시점·수치 대조. 종합 분량 1500→2500자.</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>리서치가 토론보다 느린데도 스니펫 의존·결론 미정교로 더 나쁜 결과를 내, '느린 대신 깊다'는 리서치 모드의 존재가치(근거 깊이+결론 정교화) 확보 필요.</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>리서치 모드 조사/검증/종합 파이프라인</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>v0.8.5</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>v0.8.6</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Major</t>
         </is>
       </c>
     </row>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L118"/>
+  <dimension ref="A1:L121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7326,7 +7326,6 @@
           <t>리서치 모드 1차 출처 정독 + 결론 정교화 재설계</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>조사 단계 1차 출처(공식·공시·규제기관) 직접 fetch·정독 + 최신성(현재 진행중/과거 종료) 구분 의무화. 종합 단계 증거 게이트(1차 1개 포함 출처≥2일 때만 '확정')·진행중/종료/불확실 3구간 분리·비교형 순위표. 검증 단계 인용된 1차 출처 재fetch 로 시점·수치 대조. 종합 분량 1500→2500자.</t>
@@ -7360,6 +7359,186 @@
       <c r="L118" t="inlineStr">
         <is>
           <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>리서치 분해가 부모 질문·제약을 하위질문에 누락 (제약 위반 답·조사불가)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>제약(예산·사양·수량·기간 등)이 있는 질문을 #ai-리서치에 투입</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>1. '87키 풀알루미늄 키보드 15만원 이하 추천' 투입 2. 일부 서브에이전트가 75% 키보드(87키 위반)를 섞어 추천 / '위 두 금리'·'단일 모델'처럼 맥락이 빠져 조사 불가가 됨</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>원인: 분해가 하위질문에 부모 맥락·제약을 안 실음. 수정: _build_decompose_prompt 자기완결성 지시(대명사 금지·제약 직접 명시) + _build_research_prompt(subq, question)로 원질문 전문 주입(_research_one 전달) + _build_synthesize_prompt에 '원질문 제약 모두 충족 점검·위반 후보 제외' 규칙.</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>리서치 모드 분해/조사/종합 파이프라인 정확도</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>v0.8.6</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>v0.8.7</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>리서치 종합 에이전트 실패 시 raw 에러 문자열을 종합 답변으로 방송</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Claude CLI 세션/사용 한도 소진 등 종합 단계 실패</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>1. 한도 소진 상태에서 리서치 질문 투입 2. 종합 답변 자리에 'You've hit your session limit · resets 2:10pm'가 채널로 방송됨</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>원인: synth 실패를 감지하지 않고 그대로 방송. 수정: 신규 _looks_like_failure()로 실패(한도/예외/빈값) 감지 → 에러 대신 검증 리포트로 폴백 방송. 봇 실패 래퍼는 정규식, CLI 한도는 길이무관, 일반어는 짧은 에러응답형만 매칭(오탐 방지).</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>리서치 종합 답변 채널 방송</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>v0.8.6</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>v0.8.7</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>리서치 백업 에이전트 타임아웃성 응답이 finding 으로 리포트에 노출</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>하위질문 조사에서 에이전트/백업 타임아웃(180초 등) 발생</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>1. 조사 중 백업 에이전트가 '[X-B] 응답 시간 초과 (180초)' 반환 2. 이 실패 문자열이 finding/쟁점으로 리서치 리포트에 그대로 실림</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>원인: 실패성 텍스트를 정상 finding 으로 수집. 수정: _research_one에서 _looks_like_failure로 실패성 텍스트를 finding 에서 드롭(드롭 수는 안내에 포함). F1 컨텍스트 주입으로 모호한 하위질문발 타임아웃 트리거 자체도 감소.</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>리서치 리포트/쟁점 표시</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>v0.8.6</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>v0.8.7</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Minor</t>
         </is>
       </c>
     </row>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L121"/>
+  <dimension ref="A1:L122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7542,6 +7542,66 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>토론 모드 cwd 미설정으로 Codex 가 외부 경로 평가 시 차단</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>토론 주제/질문에 봇 작업폴더 밖의 경로(평가 대상 프로젝트)를 지정</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>1. 토론 채널에서 'C:\Users\ymseo\Documents\sym-ui 경로의 프로젝트를 평가해줘' 류 주제 투입 2. Codex(codex exec -s workspace-write)가 cwd 밖 경로 접근 시도 → Windows exited -1073741502(0xC0000142 STATUS_DLL_INIT_FAILED)로 자식 프로세스 시작 실패 3. Gemini/Claude 는 정상 분석, Codex 만 '권한 문제'처럼 보이며 평가 보류</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>원인: debate 모드가 coding/bridge 와 달리 agent._cwd 를 설정하지 않아 Codex 워크스페이스가 봇 폴더에 고정. Codex 만 workspace-write 샌드박스로 cwd 밖 파일 접근이 막힘(Gemini/Claude CLI 는 무영향). 수정: DebateMode._bind_thread(thread_ts, request_text) 로 변경해 주제(start)·후속질문+원주제(followup)의 화이트리스트(ALLOWED_WORK_DIRS) 경로를 추출(security.extract_work_path)·검증(validate_work_dir)해 전 에이전트 + 백업 풀의 _cwd 로 바인딩(미지정/비허용 시 None 초기화로 스레드 간 누수 방지). extract_work_path 를 coding 과 공유화 + 자연어 suffix 보강. Codex 2라운드 교차검증 통과, 회귀 123건 통과.</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>토론 모드의 외부 경로 평가, Codex 에이전트 참여</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>v0.8.7</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>v0.8.8</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L122"/>
+  <dimension ref="A1:L123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7602,6 +7602,66 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>!bot restart 1회에 봇이 5중 spawn (재시작 재진입/중복)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>워치독 가동 중 Slack 명령 채널에서 !bot restart 전송</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>1. Slack 워치독 채널에 !bot restart 1회 전송 2. 워치독이 봇을 5개(서로 다른 PID, 일부 6ms 간격 동시) spawn 하고 '재시작 완료'를 5번 방송 3. 중복 봇은 Slack 소켓 충돌로 곧 죽고 1개로 수렴(증상은 일시적)</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>원인: 워치독은 단일 인스턴스(.watchdog.lock)·단일 스레드인데도 start_bot() 의 재진입 가드(bot_process.poll() is None)가 비원자적(TOCTOU)이라 재시작이 짧게 겹치면 중복 spawn. 수정: restart_bot 에 재진입 가드(_restart_in_progress) + 디바운스(RESTART_DEBOUNCE=10s, monotonic)로 단일 명령=단일 재시작 보장. finally 에서 auto_restart/manual_stop/_restart_in_progress 를 항상 정상 복구(예외 시 플래그 누수로 크래시 자동재시작 건너뛰던 결함도 차단). 하드닝: 단일 인스턴스 lock 을 Windows named mutex(CreateMutexW, 원자적·종료 시 자동 해제)로 전환해 중복 워치독/stale/빈창/double-takeover race 원천 소거(생성 실패 시 fail-closed). 비-Windows 폴백도 takeover 없이 fail-closed. 신규/강화 테스트 17건, 전체 405 통과. Codex 교차검증 5라운드 전부 반영(Major 4 + Minor 4), 6라운드 확인은 컴패니언 작업 정지로 보류.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>워치독 봇 재시작/단일 인스턴스 보장, Slack 명령 안정성</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>v0.8.8</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>v0.8.9</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L123"/>
+  <dimension ref="A1:L124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7662,6 +7662,66 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>mutex 전환 후 watchdog_guard 가 3분마다 헛 재기동(churn)</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>v0.8.9 named mutex 전환(lockfile 미사용) + watchdog_guard 예약작업(3분 주기) 가동</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>1. 새 워치독이 단일 인스턴스를 mutex 로만 보장하고 .watchdog.lock 을 쓰지 않음 2. watchdog_guard.is_watchdog_running()이 .watchdog.lock 의 PID 로 생존 판정 -&gt; 'dead' 오판 3. 3분마다 워치독 재기동 시도 -&gt; 매번 mutex ERROR_ALREADY_EXISTS 로 즉시 종료(churn/콘솔깜빡임)</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>원인: mutex 전환으로 lockfile 쓰기를 없앴는데 가드의 생존체크는 lockfile PID 기반이라 불일치. 수정: acquire_lock 의 Windows 경로에서 mutex 획득 성공 후 .watchdog.lock 에 PID 를 heartbeat 로 기록. 단일 인스턴스 보장은 여전히 mutex(원자적). lockfile 은 가드 정보용이라 race 무관. 가드가 live PID 를 보는 동안 lockfile 미변경 -&gt; 1회 기록으로 churn 해소. 종료/크래시 시 stale -&gt; 가드 정상 재기동. Codex 교차검증 핵심 4항목 통과(잔여 Minor 는 기존 가드 liveness 한계로 무관). test_watchdog 17건+전체 405 통과.</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>워치독 가드 재기동 동작, 콘솔 깜빡임/리소스</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>v0.8.9</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>v0.8.10</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L124"/>
+  <dimension ref="A1:L125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7722,6 +7722,66 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Claude 세션 한도 초과 메시지가 백업 미투입 + '합의된 답변'으로 방송</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Claude Code CLI 5시간 세션 한도 초과 상태에서 토론 진행</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>1. Claude 가 세션 한도 초과 상태(예: 5시간 한도 도달) 2. 슬랙 토론 채널에서 토론 시작 3. Claude 가 매 라운드 'You've hit your session limit · resets 7:50pm' 를 정상 stdout 으로 반환 4. 대체 투입 경고 없이 9라운드 내내 Claude 가 죽은 참가자(출력 0)로 남음 5. 최종 '💡 합의된 답변' 이 세션 한도 메시지 그 자체로 방송됨(질문에 대한 답이 '너 세션 한도 초과됨')</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>원인: agents/base.py _is_fatal_error 의 _FATAL_SUBSTRINGS/_FATAL_REGEX 가 세션/사용량 한도 문자열을 커버하지 않아 has_error=False -&gt; needs_replacement=False -&gt; 백업 대체 투입 미트리거. 또한 _generate_final_answer 가 교체 안 된 Claude 를 통합문 후보로 잡고 _is_bad_final_answer 도 이 메시지를 못 걸러서 방송. 수정: (1) _FATAL_SUBSTRINGS 에 'hit your session limit'/'reached your session limit'/'usage limit reached' full-phrase 추가(탐지 계층) -&gt; 백업 자동 투입 + 교체된 Claude 최종답변 후보 제외. (2) _is_bad_final_answer 에 _is_fatal_error(answer) callable 가드 방어선 추가. 신규 테스트 11건(레드-&gt;그린), 기존 회귀 없음. Codex 교차검증 통과(발견 이슈 전부 Minor/Trivial, callable 가드만 반영, 나머지는 기존 설계 트레이드오프/별개 하드닝이라 제외). v0.7.7(API 500 방송) 동형 버그.</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>토론/추가토론 모드, 최종 합의 답변, 백업 대체 투입</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>v0.8.10</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>v0.8.11</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L125"/>
+  <dimension ref="A1:L126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7782,6 +7782,66 @@
         </is>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>TestBinarySelection 4건이 dev .env 의 GEMINI_CLI_BINARY=agy 누수로 실패 (테스트 격리)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>로컬 .env 에 GEMINI_CLI_BINARY=agy 설정(봇 agy 실가동) 상태</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>1. .env 에 GEMINI_CLI_BINARY=agy 존재 2. pytest tests/test_gemini.py::TestBinarySelection 실행 3. default/empty/explicit-gemini/invalid 4건이 전부 agy 로 잡혀 실패 (agy 케이스만 우연히 .env 값과 일치해 통과)</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>원인: config.py 가 import 시 load_dotenv(override=True) 로 .env 를 읽는데, 이 테스트들이 GEMINI_CLI_BINARY 를 monkeypatch 한 뒤 importlib.reload(config) 를 하면 reload 가 load_dotenv(override=True) 를 재실행하며 dev .env 의 agy 가 monkeypatch 값을 덮어씀(테스트 격리 결함). 수정: TestBinarySelection 의 _restore_gemini_default autouse fixture 에 monkeypatch.setattr('dotenv.load_dotenv', no-op) 추가 -&gt; reload 가 .env 를 다시 읽지 않아 monkeypatch 값 유지. monkeypatch 가 fixture teardown 이후 undo 되므로 teardown reload 동안에도 패치 유효(기본값 gemini 정상 복원). production config.py 의 override=True 는 봇 정책상 의도라 미변경. TestBinarySelection 10건 통과(4실패-&gt;0), 전체 421건 통과. Codex 교차검증 통과(발견 이슈 전부 Minor/Trivial).</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>테스트 스위트(test_gemini.py), CI/로컬 개발 신뢰성</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>v0.8.11</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>v0.8.12</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L126"/>
+  <dimension ref="A1:L128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7842,6 +7842,118 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>!bot restart 한 번에 봇이 세션 수만큼(4중) 중복 spawn (크로스세션 워치독 중복)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>예약작업 2개(SlackBotWatchdog=Interactive, SlackBotWatchdogGuard=S4U 세션0)로 서로 다른 세션에 워치독이 각각 기동된 상태</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1. 로그온 세션이 다른 워치독이 2개 이상 동시 가동(실측 5개: 세션0 4 + 대화형 1) 2. Slack 에서 !bot restart 1회 입력 3. 각 워치독이 명령을 독립 처리해 봇을 하나씩 spawn + '재시작 완료, Bot 시작됨(PID)' 메시지가 서로 다른 PID 로 4번 게시</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>원인: watchdog.py 단일 인스턴스 mutex 이름이 'Local\slack_multi_agent_watchdog' 로 세션별(per-logon-session) 네임스페이스라 세션이 다른 워치독끼리 배제하지 못하고 무기한 공존(+ mutex 도입 전 6월 스테일 워치독 누적). 수정: acquire_lock 의 win32 경로에서 mutex 획득 전에 .watchdog.lock 의 PID 를 _is_pid_alive(OpenProcess, 세션 무관)로 확인해 살아있는 다른 워치독이 있으면 exit(0). Local mutex 는 동일 세션 원자성용으로 유지. Global mutex 는 S4U Limited 에서 SeCreateGlobalPrivilege 부재 시 생성 실패(fail-closed)로 워치독이 아예 안 뜰 위험이라 회피. 신규 테스트 3건 + 기존 mutex 테스트 2건 결정론화, watchdog 20건/전체 424건 통과. Codex 교차검증 PASS(로직/무회귀/Global회피 정당성). 잔여 동시 cold-start 레이스는 알려진 한계로 후속 LockFileEx 하드닝(별도 이슈) 추적. 이미 떠 있는 세션0 스테일 프로세스는 관리자 권한으로 별도 정리 필요.</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>watchdog.py 단일 인스턴스, !bot restart, 봇 중복 응답/토큰 낭비</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>v0.8.9</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>v0.8.13</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>워치독 크로스세션 단일 인스턴스 원자적 봉합 (LockFileEx)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>acquire_lock 의 크로스세션 배제를 lockfile alive-check(비원자적)에서 LockFileEx 커널 파일락(세션 무관, 특권 불필요, 프로세스 종료 시 OS 자동 해제)으로 보강해 동시 cold-start 레이스를 완전 봉합. PID 신원검증(생성시각/cmdline 대조)을 병행해 PID 재사용 오탐도 제거.</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>v0.8.13 의 lockfile alive-check 는 서로 다른 세션의 두 워치독이 stale lockfile 상태로 '동시에' cold-start 하면 둘 다 pre-check 를 통과하는 잔여 레이스가 있음(Codex Major). 정상상태는 단일 인스턴스로 수렴하나 원자적 보장은 아님.</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>watchdog.py 단일 인스턴스</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>v0.8.13</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -7921,7 +7921,6 @@
           <t>워치독 크로스세션 단일 인스턴스 원자적 봉합 (LockFileEx)</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>acquire_lock 의 크로스세션 배제를 lockfile alive-check(비원자적)에서 LockFileEx 커널 파일락(세션 무관, 특권 불필요, 프로세스 종료 시 OS 자동 해제)으로 보강해 동시 cold-start 레이스를 완전 봉합. PID 신원검증(생성시각/cmdline 대조)을 병행해 PID 재사용 오탐도 제거.</t>
@@ -7942,10 +7941,14 @@
           <t>v0.8.13</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr"/>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>v0.8.14</t>
+        </is>
+      </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L128"/>
+  <dimension ref="A1:L129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7957,6 +7957,62 @@
         </is>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>agy `-p` stdout 버그(#76) 재검증 + winpty 우회 방식 부적합 판정</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>실호출 비교 테스트 3종을 봇과 동일 조건(stdin=DEVNULL, stdout=PIPE, AGY_CLI_DISABLE_AUTO_UPDATE=1)으로 수행: A) 순수 agy -p, B) winpty agy -p, C) 현재 디스크 transcript 복구(_recover_agy_response_retry 실코드).</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>agy 1.0.16(7/3 갱신)에서 upstream #76 이 해소되어 순수 agy -p 가 비-TTY 에서도 stdout 정상 출력(4회 100% 재현). winpty 방식은 winpty 자체가 stdin 이 tty 가 아니면 'stdin is not a tty' exit 1 로 실행 거부(DEVNULL/PIPE 동일, 우회 옵션 없음) -&gt; 봇 headless subprocess 에서 부적합. 현재 디스크 복구는 stdout 결손 시에만 발동하는 무비용 안전망이라 agy 회귀 대비 존치. 결론: winpty 교체 안 함, 현행 유지, 코드 무변경.</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>agents/gemini.py(agy 백엔드 경로), 봇 응답 수신</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>v0.8.14</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>v0.8.15</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L129"/>
+  <dimension ref="A1:L131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7976,7 +7976,6 @@
           <t>agy `-p` stdout 버그(#76) 재검증 + winpty 우회 방식 부적합 판정</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>실호출 비교 테스트 3종을 봇과 동일 조건(stdin=DEVNULL, stdout=PIPE, AGY_CLI_DISABLE_AUTO_UPDATE=1)으로 수행: A) 순수 agy -p, B) winpty agy -p, C) 현재 디스크 transcript 복구(_recover_agy_response_retry 실코드).</t>
@@ -8010,6 +8009,122 @@
       <c r="L129" t="inlineStr">
         <is>
           <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Codex exec 실행 로그(exited -1073741502 등)가 Slack 답변에 누출</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>봇이 S4U 세션0(무데스크톱)에서 구동돼 Codex 셸/스킬 자식이 0xC0000142 로 크래시하는 상태(별도 이슈)</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>1. 봇이 S4U 세션에서 가동 2. #ai-토론에 Codex 가 스킬/셸을 쓰게 되는 질문 입력(예: 'agy나 codex는 최상위 전역 메모리 기능이 없어?') 3. Codex 답변에 `Output:` 빈 블록, `exited -1073741502 in 31ms:`, `mcp: openaiDeveloperDocs/search_openai_docs (completed)` 조각이 그대로 노출됨</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>원인: _clean_codex_output 노이즈 필터가 `exited 0/1 in` 리터럴만 잡아 음수 exit code(-1073741502=0xC0000142 STATUS_DLL_INIT_FAILED)·`Output:` 단독·`mcp:` 라인을 못 걸렀음. 수정: `_CODEX_EXEC_LOG_LINE` 앵커드 정규식(음수·소수 duration, MCP started/completed/failed/error, Output:) 신설 후 정제 루프에 적용. 산문 오삭제 위험 있던 기존 `exited 0/1 in` 서브스트링 리터럴은 제거하고 정규식이 전담(^...$ 앵커라 '함수의 Output: 42'·'process exited 0 in my demo' 같은 본문은 보존). 회귀 테스트 7건 + 전체 432건 통과. Codex 교차검증 PASS(제안 3건 반영).</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>토론/리서치 모드 Codex 답변 표시(Slack), agents/codex.py</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>BE v0.8.15</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>BE v0.8.16</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>봇이 S4U 세션0(무데스크톱) 구동 시 Codex 셸/스킬 자식이 0xC0000142 로 전멸 → 무근거 답변</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>watchdog_guard(S4U, 세션0)가 단일 인스턴스 락을 먼저 잡아 봇을 세션0에서 spawn 한 상태</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>1. 봇이 S4U 가드 경로로 세션0에 기동 2. Codex 가 셸/스킬/웹 도구를 쓰려는 토론 질문 입력 3. Codex 의 모든 콘솔 자식 spawn 이 `exited -1073741502`(STATUS_DLL_INIT_FAILED)로 즉사, in-process MCP 만 성공 4. Codex 가 도구 없이 무근거로 답하며 'Claude 의견에 동의'로 얼버무림</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>원인: v0.8.1 에서 cmd 창 깜빡임 제거 목적으로 봇을 S4U 비대화형(세션0)으로 옮겼는데, 세션0 엔 데스크톱/윈도우스테이션이 없어 PowerShell·스킬 러너 등 콘솔 자식 프로세스가 DLL init 에 실패(0xC0000142). Interactive 세션에선 정상(활성 세션 A/B 실측: workspace-write·danger-full-access 둘 다 무크래시). 어느 워치독이 단일 락을 먼저 잡느냐로 세션이 갈림(watchdog_guard.start_watchdog 가 이기면 봇 트리가 세션0). 수정: 아키텍처 결정 대기(봇을 항상 데스크톱 세션에서 구동 vs 깜빡임 감수). 표면 로그 누출은 v0.8.16 필터로 봉합.</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>토론/리서치 모드 Codex 도구 사용(셸/스킬/웹), watchdog_guard.py·watchdog.py 세션, Codex 답변 품질</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>BE v0.8.1</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Major</t>
         </is>
       </c>
     </row>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -8103,7 +8103,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>원인: v0.8.1 에서 cmd 창 깜빡임 제거 목적으로 봇을 S4U 비대화형(세션0)으로 옮겼는데, 세션0 엔 데스크톱/윈도우스테이션이 없어 PowerShell·스킬 러너 등 콘솔 자식 프로세스가 DLL init 에 실패(0xC0000142). Interactive 세션에선 정상(활성 세션 A/B 실측: workspace-write·danger-full-access 둘 다 무크래시). 어느 워치독이 단일 락을 먼저 잡느냐로 세션이 갈림(watchdog_guard.start_watchdog 가 이기면 봇 트리가 세션0). 수정: 아키텍처 결정 대기(봇을 항상 데스크톱 세션에서 구동 vs 깜빡임 감수). 표면 로그 누출은 v0.8.16 필터로 봉합.</t>
+          <t>원인: v0.8.1 에서 cmd 창 깜빡임 제거 목적으로 봇을 S4U 비대화형(세션0)으로 옮겼는데, 세션0 엔 데스크톱/윈도우스테이션이 없어 PowerShell·스킬 러너 등 콘솔 자식 프로세스가 DLL init 에 실패(0xC0000142). Interactive 세션에선 정상(활성 세션 A/B 실측: workspace-write·danger-full-access 둘 다 무크래시). 어느 워치독이 단일 락을 먼저 잡느냐로 세션이 갈림(watchdog_guard.start_watchdog 가 이기면 봇 트리가 세션0). 수정: 아키텍처 결정 대기(봇을 항상 데스크톱 세션에서 구동 vs 깜빡임 감수). 표면 로그 누출은 v0.8.16 필터로 봉합. [해결 v0.8.17 / Option 1: S4U(무깜빡임) 유지 + 토론/리서치 Codex 에 avoid_shell 지시 주입해 로컬 셸 시도 억제. Codex 는 openaiDeveloperDocs MCP·지식으로 그라운딩. 코딩 모드 셸 세션0 미동작은 드문 용도라 수용(완전 복구는 Option 2=대화형 상주, 깜빡임 부활).]</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8116,10 +8116,14 @@
           <t>BE v0.8.1</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr"/>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>BE v0.8.17</t>
+        </is>
+      </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L131"/>
+  <dimension ref="A1:L132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8132,6 +8132,66 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>재기동 후 Codex 가 원격 MCP 일시적 HTTP 503 로그를 답변에 누출 + fatal 오탐으로 백업 교체</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>봇이 재기동된 직후, 원격 MCP openaiDeveloperDocs(url=developers.openai.com/mcp) 엔드포인트가 일시적으로 503 반환</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>1. !bot restart 로 봇 재기동(세션0 유지) 2. 토론 질문 입력(예: 오늘 매수할만한 주식 추천) 3. Codex 답변 첫 줄에 `2026-...Z ERROR rmcp::transport::worker: worker quit with fatal: ... HTTP 503: upstream connect error ... when send initialized notification` 누출 4. 봇이 그 'HTTP 503' 을 Codex fatal 로 오탐 → 'Codex 오류 감지 → Gemini-B 대체 투입' 으로 교체(Codex 는 실제로 유효 추천을 냈음)</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>원인: (1) v0.8.16 필터는 exec-log/Output:/mcp: 형식만 잡아 Rust tracing 로그(rmcp transport 오류)를 못 걸러 누출. (2) 봇은 progress 경로에서 정제 전 raw 로 _is_fatal_error 판정 → 로그의 'HTTP 503' 이 _FATAL_REGEX 에 걸려 has_error=True → 유효 답변인데도 백업 교체. openaiDeveloperDocs 는 원격이라 세션 무관, 503 은 재기동 직후 일시적 blip(조사 시점 엔드포인트 HTTP 200 정상). 수정: `_CODEX_TRACING_LOG` 정규식(ISO8601 타임스탬프+LEVEL target: 형식)으로 tracing 로그 라인 필터 + CodexAgent.ask_with_progress 가 has_error 를 정제된 답변 기준으로 재판정(cleaned 비어있지 않고 timed_out 아닐 때만; 진짜 API fatal 은 필터가 안 지우므로 유지). 회귀 6건 + 전체 443건 통과. Codex 교차검증 반영(정규식 엄격화, 넓은 rmcp:: substring 제거).</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>토론/리서치 모드 Codex 답변 표시 + 백업 교체 로직, agents/codex.py</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>BE v0.8.17</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>BE v0.8.18</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L132"/>
+  <dimension ref="A1:L142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8192,6 +8192,601 @@
         </is>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>에이전트 실패 응답 원문(세션 한도/타임아웃)이 정상 답변 말풍선으로 게시됨</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Claude CLI 가 세션 한도에 걸린 상태(You've hit your session limit) 또는 응답 타임아웃</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>1. 토론 채널에 질문 입력 2. 라운드 1에서 Claude 가 세션 한도 문구를 stdout 으로 반환 3. Slack 에 '🟠 [Claude] You've hit your session limit · resets 1:20am / 출력 0 | $0.000' 이 정상 답변처럼 게시됨 4. 그 다음에야 '⚠️ Claude 오류 감지 → Codex-B 대체 투입' 경고가 붙음. 코딩 모드도 동일('[Claude] 응답 대기 시간 초과 (574초)' 말풍선). 최근 대화 실측 6회</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>원인: modes/debate.py 의 _ask_and_post() 가 응답을 먼저 post 하고, 오류 판정 루프는 asyncio.gather() 완료 후 별도로 돌았다. agent.has_error 는 post 시점에 이미 True 인데 post 경로가 그 플래그를 조회하지 않는 구조. modes/coding.py 의 _ask_with_backup 은 아예 실패 응답을 명시적으로 post 했다. 수정: post 전에 needs_replacement 검사 → 실패 응답 비게시, history/round_consensuses 에서도 제외(다음 라운드 프롬프트 오염 방지), 백업 없으면 '대체 에이전트 없음' 고지</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>토론 모드 전 라운드, 코딩 모드 전 Phase, Slack 답변 표시</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>BE v0.8.18</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>BE v0.8.19</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>폴백 시 동일 사건에 경고 2개('대체 투입' + '이후 라운드부터 교체') 중복 게시</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>에이전트 오류/타임아웃으로 백업 투입이 발생</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>1. 토론 중 Claude 장애 발생 2. '⚠️ Claude 오류 감지 → Codex-B 대체 투입' 게시 3. 바로 이어서 '⚠️ Claude 오류 감지 → 이후 라운드부터 Codex-B 교체' 가 또 게시됨(항상 쌍)</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>원인: 폴백 루프가 경고 1을 post 하고 같은 iteration 끝에서 호출하는 _replace_agent() 가 경고 2를 또 post. 수정: _replace_agent 의 post 를 제거하고 '대체 투입 (이후 라운드도 X)' 한 줄로 병합</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>토론/코딩 모드 Slack 메시지</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>BE v0.8.18</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>BE v0.8.19</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>후속 질문마다 교체 상태가 초기화되어 세션 한도로 죽은 에이전트를 매번 재호출</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>세션 한도 등으로 이미 백업 교체된 에이전트가 있는 토론 스레드에서 추가 질문</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>1. 토론 중 Claude 세션 한도 → Codex-B 교체 2. 같은 스레드에 추가 질문 입력 3. 추가 토론 라운드 1에서 Claude 가 다시 호출되어 같은 세션 한도 에러가 또 노출되고 폴백 절차를 처음부터 반복 4. 실측: 콜드브루 스레드에서 22:39/22:50/22:56 3회, 컵라면 스레드 2회</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>원인: slack_bot.py:194,205 가 메시지마다 DebateMode 를 새로 생성해 인스턴스 속성인 self._replaced 가 스레드 안에서 유지되지 않음. 세션 한도는 몇 시간 지속되는데 매번 재시도. 수정: 모듈 전역 _THREAD_REPLACED[thread_ts] = {원본: 백업} 으로 기억하고 _bind_thread 에서 복원해 첫 라운드부터 백업으로 시작. 상한 200스레드(FIFO 폐기). 프로세스 재기동 시 초기화 = 원본 재시도</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>토론 모드 후속 질문(followup), 응답 지연 + 에러 반복 노출</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>BE v0.8.18</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>BE v0.8.19</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>합의 조기 종료 불가: 어휘 발산 판정이 상시 True 라 만장일치에도 교전 라운드 강제</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>1. 토론 질문 입력 2. 라운드 2에서 3/3 전원 동의(agree=true)인데도 종료하지 않고 라운드 3 진행 3. bot_output.log 실측: 라운드 판정 639건 중 diverged=True 606건(94.8%), 3/3 만장일치 354건도 발산 판정. 축구/AI비교 스레드가 불필요하게 3라운드까지 감(라운드당 CLI 3회 호출 낭비)</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>원인: _summaries_diverge() 가 한국어를 어절 단위로 자르는 토크나이저로 Jaccard 를 재고 최소 페어값을 썼다. 실측 보정 결과 어휘 유사도로는 합의/불합의 구분이 불가능하다: 같은 결론을 다른 표현으로 쓴 진짜 합의가 bigram 0.027 인데 서로 배타적 결론(라멘/파스타/초밥)이 0.045 로 더 높았다(토크나이저·임계값 조정으로 해결 불가). 수정: 유사도는 '수렴 확인'에만 사용 → 수렴 시 라운드 1 즉시 종료 허용, 그 외에는 상호 검토 1회(라운드 2) 후 종료. 교전 라운드는 CONSENSUS.disagreements 에 구조적 쟁점이 기록된 경우에만 1회 강제. dead config CONSENSUS_EARLY_ROUNDS(import 만 되고 미사용) 제거</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>토론/추가 토론 종료 판정, 라운드 수·응답 지연·CLI 비용</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>BE v0.8.18</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>BE v0.8.19</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Codex 툴콜 preamble('먼저 ~를 확인하겠습니다')이 최종 답변 앞에 노출</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Codex 가 웹 검색 등 툴을 호출하는 질문</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>1. 토론 채널에 가격/시세 등 검색이 필요한 질문 입력 2. Codex 답변이 '현재 판매처·가격을 먼저 확인하겠습니다. 있어요. 오사카픽은...' 처럼 준비 문장으로 시작 3. 실측: 에이전트 발언 121건 중 32건(26%), 거의 전부 Codex 계열</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>원인: agents/codex.py 에 최종 메시지 추출 로직이 없어 codex exec 의 stdout 전량을 누적한 뒤 라인 단위 노이즈 필터만 적용했다. 필터는 CLI 헤더/exec 로그 같은 구조적 노이즈만 지우고 모델이 생성한 산문은 통과시키므로, 툴 호출 직전 preamble 이 그대로 남는다(Claude 는 stream-json 의 result 이벤트만 채택). 수정: codex exec -o FILE 로 마지막 에이전트 메시지만 받아 답변으로 채택. stdout 은 진행 표시용으로 계속 읽고, 파일 부재 시 기존 정제 경로로 폴백, 타임아웃 시 잔여 파일 무시. 실제 CLI 로 검증 완료</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>토론/리서치/코딩 모드의 Codex·Codex-B 답변 본문</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>BE v0.8.18</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>BE v0.8.19</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>폴백으로 동일 엔진 2인 구성이 되면 결론에 고지</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Claude 장애 시 폴백이 Codex-B(= Codex 와 동일 CLI/모델)라 3자 중 2인이 같은 엔진이 되는데도 '전원 합의'가 그대로 선언됐다. 결론 브로드캐스트에 '동일 엔진 2인 구성(Codex, Codex-B) - 폴백으로 계열이 겹쳐 합의가 실제보다 강해 보일 수 있습니다' 고지를 추가</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>3계열(claude/codex/gemini)을 3에이전트가 모두 점유한 상태에서 하나가 죽으면 살아있는 계열의 복제본을 투입할 수밖에 없다(같은 계열 백업은 세션 한도를 공유하므로 더 나쁨). 구조적으로 피할 수 없다면 숨기지 말고 명시해야 사용자가 합의 강도를 과신하지 않는다. 백업 선택 로직 자체는 유지</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>토론 결론 메시지(전원 합의/다수 합의/최대 라운드 등 모든 결론 경로)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>BE v0.8.18</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>BE v0.8.19</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>백업까지 실패하는 이중 장애에서 백업의 에러 원문이 답변으로 게시됨</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>1차 에이전트가 세션 한도/타임아웃으로 실패해 백업이 투입됐는데 백업도 실패</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>1. Claude 세션 한도 → Codex-B 대체 투입 2. Codex-B 도 타임아웃 3. '[Codex-B] 응답 시간 초과 (180초)' 가 정상 답변 말풍선으로 게시됨. 코딩 모드 Phase 3(테스트 작성)는 1차 실패 응답조차 게시 가드가 없었음(5월 스레드에서 Gemini node-pty 경로 에러, Claude 574초 타임아웃이 그대로 노출)</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>원인: 1차 실패만 막고 백업 응답은 needs_replacement 검사 없이 게시·history·consensus 에 추가했다. 코딩 Phase 3(modes/coding.py)는 세 에이전트 결과를 먼저 게시한 뒤 교체를 검사하는 구조였다. 수정: 백업 응답도 실패 시 원문 대신 '백업도 실패' 만 고지하고 그 슬롯 없이 진행. 코딩 모드의 모든 게시 지점(_ask_with_backup, 병렬 경로 2곳, Phase 3)에 동일 가드 적용. Codex 교차검증 [1][2]</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>토론/코딩 모드 이중 장애 경로, Slack 답변 표시</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>BE v0.8.18</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>BE v0.8.19</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>백업 풀 소진 시 이미 투입된 백업 인스턴스를 중복 삽입(동일 객체 동시 호출 위험)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>세 에이전트가 모두 백업으로 교체된 상태에서 백업 중 하나가 또 실패</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>1. Claude/Codex/Gemini 가 순차로 모두 장애 → 백업 3개가 모두 self.agents 에 투입 2. 투입된 백업이 또 실패 3. _get_backup() 이 후보 소진 시 풀 전체로 되돌아가 이미 agents 에 있는 인스턴스를 반환 → 같은 객체가 리스트에 2번 들어가고 한 인스턴스가 동시에 호출될 수 있음</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>원인: _get_backup() 의 `if not candidates: candidates = list(self._backup_pool)` 폴백이 중복을 허용했다(기존 코드부터 있던 잠재 결함). 수정: 소진 시 None 을 반환하고 호출부가 '대체 에이전트 없음 (이번 라운드 제외)' 을 고지하도록 변경. Codex 교차검증 [1]</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>토론 모드 다중 장애 경로, 에이전트 리스트 무결성</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>BE v0.8.18</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>BE v0.8.19</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>codex -o 최종 메시지 파일 경로를 인스턴스 필드에 저장해 동시 호출 간 충돌/누수</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>같은 에이전트 인스턴스가 동시에 두 번 호출되는 경우(리서치 분담 조사에서 소주제 4개를 에이전트 3개에 배분하면 한 인스턴스에 2건이 동시 배정)</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>1. 리서치 모드에서 소주제 4개가 3개 에이전트에 분배 2. Codex 인스턴스가 2건을 동시에 실행 3. 두 호출이 self._last_msg_path 를 서로 덮어써, 한 호출이 다른 호출의 출력 파일을 읽거나 삭제할 수 있음 4. 타임아웃/취소 경로에서는 .last.md 파일이 임시 폴더에 잔존</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>원인: v0.8.19 초안이 `-o` 경로를 인스턴스 필드(self._last_msg_path)로 관리했다. 수정: 경로를 호출별 prompt tmp 에서 파생(&lt;tmp&gt;.last.md)하고, AgentBase 에 _finalize_output/_cleanup_artifact 훅을 추가해 정상/타임아웃/취소/예외 모든 경로의 finally 에서 삭제. 실제 CLI 로 잔존 파일 0건 확인. Codex 교차검증 [3]</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Codex 계열 에이전트 전 모드(특히 리서치 병렬 조사), 임시 파일</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>BE v0.8.19(커밋 전)</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>BE v0.8.19</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>스레드 교체 기록 eviction 이 현재 스레드의 앞선 기록을 삭제 + 무잠금 경합</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>_THREAD_REPLACED 가 상한(200)에 도달한 상태에서 기존 스레드에 두 번째 교체가 발생</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>1. 가장 오래된 스레드에 Claude→Codex-B 교체가 기록된 상태 2. 같은 스레드에서 Codex 도 교체 3. 상한 초과 폐기가 가장 오래된 키(=바로 그 스레드)를 먼저 지워 Claude 기록이 소실 4. 다음 후속 질문에서 죽은 Claude 가 다시 투입됨</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>원인: v0.8.19 초안이 삽입 전 무조건 오래된 키를 폐기했다. 또한 토론은 스레드마다 별도 OS 스레드/이벤트 루프에서 돌아 module-global dict 의 read-modify-write 가 경합 위험. 수정: 새 키를 넣을 때만 폐기하고, threading.Lock 으로 get/set/pop 직렬화. Codex 교차검증 [4]</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>토론 모드 후속 질문의 에이전트 교체 유지</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>BE v0.8.19(커밋 전)</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>BE v0.8.19</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L142"/>
+  <dimension ref="A1:L153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8787,6 +8787,680 @@
         </is>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>코딩 수정 루프가 에이전트 실패 원문을 테스트 결과로 읽어 가짜 이슈를 만들고 코드를 산문으로 덮어씀 (재귀 오염)</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>코딩 모드 Phase 3(테스트 3병렬)에서 Claude 가 타임아웃하고 그 백업까지 실패한 상태</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>1. #ai-코딩 채널에 코딩 요청 2. Phase 3 에서 Claude 가 타임아웃 -&gt; "[Claude] 응답 대기 시간 초과 (574초 무응답)" 반환 3. 백업도 실패 4. 그 실패 문구가 all_tests 에 그대로 포함돼 Codex 이슈 판단 프롬프트로 전달됨 5. Codex 가 "이슈 있음: 타임아웃으로 테스트가 완료되지 않아 판단 불가" 를 이슈로 보고 6. 그 가짜 이슈로 Claude 에게 코드 수정 요청 -&gt; Claude 가 코드 대신 산문 반환 7. 산문이 current_code 가 되어 "[수정된 코드]" 로 게시되고 다음 라운드에 "기존 코드" 로 재투입</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>원인: BaseAgent 는 타임아웃/치명적 오류를 예외가 아니라 평범한 문자열로 반환하는데(agents/base.py:101,141,191,201), v0.8.19 는 이 실패 원문의 "게시"만 막고 "하류 전달"은 막지 않았다. modes/coding.py:871 이 실패한 슬롯의 문자열까지 all_tests 에 이어붙였고, 877 이 그걸 테스트 결과라며 Codex 에 넘겼다. 수정: (1) 실패한 Phase 3 슬롯을 None 으로 폐기하고 성공분만 all_tests 로 합침 (2) 테스트 결과 0건이면 이슈 판단 자체를 건너뜀 (3) Codex 이슈 판단이 실패하면 원문을 이슈로 삼지 않고 루프 중단 (4) Claude 수정 호출이 실패하면 current_code 를 덮어쓰지 않고 직전 코드 유지</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>코딩 모드 Phase 3 + 이슈 수정 루프 + 최종 보고서. 코드 산출물이 산문으로 대체되어 사용자에게 게시됨</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>BE v0.8.19</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>BE v0.8.20</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Phase 1 주/백업 이중 실패 시 실패 문구가 claude_code 가 되어 그대로 리뷰/테스트됨</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Phase 1 에서 Claude 와 그 백업이 모두 실패(타임아웃/세션 한도)한 상태</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>1. 코딩 요청 2. Phase 1 Claude 타임아웃 -&gt; 백업 투입 -&gt; 백업도 세션 한도로 실패 3. _ask_with_backup 이 "[Claude] 응답을 받지 못했습니다 (백업 ... 도 실패)." 를 반환 4. 이 문구가 claude_code 로 Phase 2 리뷰 프롬프트와 Phase 3 테스트 프롬프트에 "코드" 로 삽입됨. 백업이 아예 없는 경우엔 실패 원문이 그대로 반환돼 답변으로 게시까지 됨</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>원인: modes/coding.py 의 Phase 1 호출부(_start_inner, followup 재개)가 _ask_with_backup 반환값의 성공 여부(needs_replacement)를 확인하지 않고 무조건 Phase 2/3 로 넘겼다. 또한 _ask_with_backup 은 백업 풀이 소진되면 실패 원문을 그대로 돌려줬다. 수정: Phase 1 실패 시 "코드 생성 실패 -&gt; 리뷰/테스트 단계 중단" 을 고지하고 후속 단계 진입을 차단. _ask_with_backup 은 백업이 없어도 실패 원문 대신 정제 문구를 반환하고 needs_replacement 로 실패를 알림</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>코딩 모드 Phase 1 -&gt; Phase 2/3 전이, 백업 풀 소진 경로</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>BE v0.8.19</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>BE v0.8.20</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>병렬 모드에서 백업이 없는 실패 에이전트의 응답 원문이 최종 요약 프롬프트로 유입</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>코딩 병렬 모드에서 한 에이전트가 실패하고 그 백업이 없는 상태</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>1. 코딩 병렬 모드 실행 2. Claude 타임아웃, 백업 풀 소진 3. modes/coding.py:669-670 이 실패 원문을 final_responses 에 그대로 append 4. 678-679 가 그걸 "[Claude 결과]" 로 요약 프롬프트에 삽입 -&gt; Codex 가 타임아웃 문구를 작업 결과로 읽고 요약</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>원인: 백업이 존재할 때만 continue 로 빠져나가고, 백업이 없으면 실패한 에이전트와 그 실패 원문이 그대로 final_agents/final_responses 에 담겼다. 수정: 백업이 없거나 백업까지 실패하면 결과 없이 제외하고 사유를 고지. 전원 실패면 빈 요약을 요청하지 않고 중단</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>코딩 병렬 모드 최종 보고서</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>BE v0.8.19</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>BE v0.8.20</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>최종 보고서 생성이 실패하면 그 실패 원문이 "최종 보고서" 로 방송됨</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>최종 보고서 작성 단계에서 Codex 가 타임아웃/오류로 실패한 상태</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>1. 코딩 모드 실행 2. 마지막 보고서 생성 호출에서 Codex 타임아웃 3. 반환된 "[Codex] 응답 시간 초과 (300초)" 가 그대로 "📋 최종 보고서 (Codex)" 로 broadcast 됨 (병렬 모드도 동일)</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>원인: 보고서 호출 결과의 needs_replacement 를 확인하지 않고 무조건 방송했다. 수정: 실패 시 방송하지 않고 "최종 보고서 생성 실패" 고지로 대체. 아울러 None(호출 실패)과 ""(내용 없는 정상 응답)을 구분하는 _test_summary() 를 도입해 보고서가 둘을 혼동하지 않게 함</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>코딩 모드/병렬 모드 최종 보고서 방송</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>BE v0.8.19</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>BE v0.8.20</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>타임아웃 메시지가 실제보다 60초 적은 "574초" 로 표기되고 한도(600초)도 초과</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>코딩 모드에서 Claude 가 도구 호출 중 60초 이상 무응답인 상태</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>1. 코딩 모드 실행 2. Claude 가 스트리밍 중 장시간 무응답 3. 전체 한도 600초를 넘겨 종료되는데 Slack 에는 "[Claude] 응답 대기 시간 초과 (574초)" 로 게시됨 (실제 경과는 634초)</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>원인: agents/claude.py(및 동형인 gemini.py) 읽기 루프가 elapsed 를 루프 진입 시점에 재고, readline 을 고정 60초 기다린 뒤 그 stale 값을 메시지에 찍었다. 한도 검사도 루프 진입 시점에만 해서 readline_timeout(60초) 만큼 한도를 넘겼다(실효 상한 660초). 수정: readline 대기를 min(STREAM_IDLE_TIMEOUT, 남은 예산) 으로 자르고, 보고 직전 elapsed 를 재측정. 메시지에 한도를 병기(응답 시간 초과 (634초 / 한도 600초)). start_time 도 spawn 전으로 옮겨 spawn/stdin drain 시간을 예산에 포함(Codex 지적 반영)</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>코딩/토론/리서치 전 모드의 스트리밍 타임아웃 메시지 및 실제 상한</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>BE v0.8.20</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>BE v0.8.21</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>같은 timeout 인자가 에이전트마다 다른 예산을 의미 (Codex 300초 vs Claude 660초)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>1. 코딩 모드에서 timeout=CLI_TIMEOUT_CODING(300) 을 모든 에이전트에 동일하게 전달 2. 실제로는 base(Codex)=300초, Claude=600(+60)초, Gemini=600초/가드 750초로 제각각 3. 한 실행에 "[Claude] 응답 시간 초과 (300초)" 와 "(574초)" 가 동시에 찍힘</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>원인: 스트리밍 구현이 내부에서 timeout 을 조용히 t*2 로 늘렸고 base 구현은 안 늘렸다. 수정: 숨은 배수 제거. timeout 이 곧 예산. 모드별 예산을 상수로 승격 (CLI_TIMEOUT 180-&gt;360, CLI_TIMEOUT_CODING 300-&gt;600, CLI_TIMEOUT_RESEARCH 180 신설). 실효 예산은 의도적으로 조정됨: 코딩 Claude 660-&gt;600(축소), 코딩 Codex 300-&gt;600(확대). Codex 확대는 의도 - 예전엔 절반 예산이라 정상 장시간 작업 중 혼자 먼저 타임아웃 나 불필요하게 백업 교체됐다. 토론 라운드 체감 상한은 420-&gt;360초로 오히려 감소</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>전 모드 에이전트 호출 예산, 백업 교체 빈도</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>BE v0.8.20</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>BE v0.8.21</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>한 에이전트의 타임아웃이 병렬 실행 중인 형제 에이전트의 프로세스까지 kill</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>여러 에이전트가 asyncio.gather 로 병렬 실행 중 (코딩 Phase 3, 리서치 분담 조사)</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>1. 코딩 Phase 3 에서 Codex/Claude/Gemini 가 같은 thread_ts 로 병렬 실행 2. 그 중 하나가 타임아웃 3. _kill_registered_processes() 가 thread_ts 에 등록된 모든 프로세스를 죽여 멀쩡히 돌던 나머지 에이전트도 동반 실패 4. 테스트 결과 0건 -&gt; Codex 가짜 이슈 -&gt; 수정 루프 헛돎</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>원인: cancel.active_processes 가 thread_ts 단위 레지스트리인데 타임아웃 정리가 그걸 그대로 순회해 전부 죽였다. 모든 에이전트는 같은 _current_thread_ts 를 공유한다. 게다가 리서치는 하위질문을 라운드로빈 배정하므로 같은 인스턴스가 동시에 2건을 맡기도 한다(4문항/3에이전트). 수정: contextvars.ContextVar + AgentBase._call_scope() 로 kill 사정거리를 호출 단위로 축소. 사용자 취소(/cancel)는 기존대로 스레드 전체 kill 유지</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>코딩 Phase 3, 리서치 분담 조사, 토론 라운드 (병렬 실행 전 구간)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>BE v0.8.20</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>BE v0.8.21</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Claude 스트리밍에 외부 가드가 없어 읽기 루프 밖 hang 이 영구 대기</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>stdin drain 이 막히거나 proc.wait() 이 복귀하지 않는 상태</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>1. Claude CLI 가 stdin 을 읽지 않아 파이프 버퍼가 참 2. await proc.stdin.drain() 이 영구 블록 3. 읽기 루프에 진입조차 못 해 내부 데드라인 검사가 발동하지 않음 4. 봇 정지</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>원인: 내부 데드라인은 읽기 루프 안에서만 검사된다. 루프 밖 await(stdin drain, proc.wait)은 그 검사에 도달하지 못한다. Gemini 는 v0.7.3.2 에서 외부 가드를 받았지만 Claude 는 무방비였다. 수정: base.ask_with_progress 가 _stream_once 를 t*STREAM_GUARD_FACTOR(1.25) 로 감싼다. Claude 는 _stream_once 만 오버라이드하도록 정리했고 Codex 는 super() 위임이라 자동 적용. 상한은 정상 t, 병리적 hang 시 t*1.25</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Claude/Codex 스트리밍 호출 (코딩 전 Phase, 토론 라운드)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>BE v0.8.20</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>BE v0.8.21</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>외부 가드 취소 시 살아있는 CLI 를 죽이기 전에 부산물을 지워 임시 폴더에 파일 누수</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>외부 가드가 발동해 _stream_once 코루틴이 cancel 되는 상태</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>1. 외부 가드(asyncio.wait_for) 타임아웃 2. wait_for 가 내부 Task 를 cancel 하고 그 Task 의 finally 가 먼저 완료됨 3. 그 finally 가 아직 살아있는 CLI 의 -o &lt;tmp&gt;.last.md 부산물과 프롬프트 파일을 삭제 4. 그 뒤에야 호출부 except 가 프로세스를 kill 5. 삭제와 kill 사이에 살아있는 writer 가 파일을 다시 써서 임시 폴더에 남음</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>원인: 정리 순서가 (파일 삭제 -&gt; 프로세스 kill) 이었다. asyncio.wait_for 는 내부 Task 의 finally 가 끝난 뒤에야 호출부로 제어를 넘기므로, 파일 정리 시점에 CLI 가 아직 살아있다. 수정: _kill_if_alive() 를 파일 정리 앞에 배치해 writer 를 먼저 죽인다(kill_process_tree 는 동기 함수라 cancel 중인 finally 안에서도 안전 - 여기서 await 하면 CancelledError 가 재발생해 정리가 중단된다). Codex 교차검증 지적 반영</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>CodexAgent 의 -o 최종 메시지 파일, 전 에이전트의 프롬프트 임시 파일</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>BE v0.8.20</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>BE v0.8.21</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>코딩 모드 백업 에이전트가 primary 보다 짧은 예산으로 호출됨</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>primary 에이전트가 타임아웃/오류로 백업 교체가 트리거된 상태</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>1. 코딩 모드에서 primary 가 코딩 예산(600초)을 다 쓰고 타임아웃 2. _ask_with_backup 이 backup.ask(prompt) 를 timeout 인자 없이 호출 3. 백업은 기본 예산(CLI_TIMEOUT)만 받아 primary 보다 짧은 시간 안에 끝내야 함</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>원인: modes/coding.py 의 백업 호출만 timeout 인자를 빠뜨렸다(다른 백업 경로는 CLI_TIMEOUT_CODING 을 넘긴다). primary 가 코딩 예산으로도 못 끝낸 일을 더 짧은 예산으로 시키는 꼴이라 이중 실패(백업도 실패) 확률만 올라간다. 수정: timeout=CLI_TIMEOUT_CODING 명시. 재시도 정책 점검 결과 타임아웃 자체는 재시도하지 않고(같은 예산 재실행은 실패 시간만 2배) 곧바로 백업 교체하되, 백업은 primary 와 같은 예산을 받는 것으로 확정</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>코딩 모드 백업 교체 경로</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>BE v0.8.20</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>BE v0.8.21</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>에이전트 상태 플래그(timed_out/has_error/last_usage)가 인스턴스 공유라 병렬 호출에 취약</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>리서치가 같은 에이전트 인스턴스를 병렬 호출하는데(라운드로빈 배정: 4문항/3에이전트) timed_out/has_error/last_usage 는 인스턴스 속성이다. 호출별 상태 객체로 분리하거나 호출 결과에 상태를 함께 반환해 공유 플래그 판정을 제거해야 한다.</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>v0.8.21 에서 프로세스 kill 사정거리는 호출 단위로 좁혔으나 상태 플래그는 여전히 인스턴스 공유다. 현재 호출부는 ask() 반환 직후 await 없이 곧바로 플래그를 읽으므로(이벤트 루프가 그 사이에 다른 코루틴을 끼워넣지 못함) 실제 트리거는 확인되지 않았다. 다만 호출부에 await 가 하나만 끼어들면 곧바로 오판(한 호출의 실패가 다른 호출의 백업 교체를 유발)으로 이어지는 구조적 취약점이라 선제 정리가 필요하다. Codex 교차검증 지적 반영</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>리서치 분담 조사, 향후 동일 인스턴스 병렬 호출을 추가하는 모든 경로</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>BE v0.8.21</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L153"/>
+  <dimension ref="A1:L142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8787,680 +8787,6 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>코딩 수정 루프가 에이전트 실패 원문을 테스트 결과로 읽어 가짜 이슈를 만들고 코드를 산문으로 덮어씀 (재귀 오염)</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>코딩 모드 Phase 3(테스트 3병렬)에서 Claude 가 타임아웃하고 그 백업까지 실패한 상태</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>1. #ai-코딩 채널에 코딩 요청 2. Phase 3 에서 Claude 가 타임아웃 -&gt; "[Claude] 응답 대기 시간 초과 (574초 무응답)" 반환 3. 백업도 실패 4. 그 실패 문구가 all_tests 에 그대로 포함돼 Codex 이슈 판단 프롬프트로 전달됨 5. Codex 가 "이슈 있음: 타임아웃으로 테스트가 완료되지 않아 판단 불가" 를 이슈로 보고 6. 그 가짜 이슈로 Claude 에게 코드 수정 요청 -&gt; Claude 가 코드 대신 산문 반환 7. 산문이 current_code 가 되어 "[수정된 코드]" 로 게시되고 다음 라운드에 "기존 코드" 로 재투입</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>원인: BaseAgent 는 타임아웃/치명적 오류를 예외가 아니라 평범한 문자열로 반환하는데(agents/base.py:101,141,191,201), v0.8.19 는 이 실패 원문의 "게시"만 막고 "하류 전달"은 막지 않았다. modes/coding.py:871 이 실패한 슬롯의 문자열까지 all_tests 에 이어붙였고, 877 이 그걸 테스트 결과라며 Codex 에 넘겼다. 수정: (1) 실패한 Phase 3 슬롯을 None 으로 폐기하고 성공분만 all_tests 로 합침 (2) 테스트 결과 0건이면 이슈 판단 자체를 건너뜀 (3) Codex 이슈 판단이 실패하면 원문을 이슈로 삼지 않고 루프 중단 (4) Claude 수정 호출이 실패하면 current_code 를 덮어쓰지 않고 직전 코드 유지</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>코딩 모드 Phase 3 + 이슈 수정 루프 + 최종 보고서. 코드 산출물이 산문으로 대체되어 사용자에게 게시됨</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>BE v0.8.19</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>BE v0.8.20</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Phase 1 주/백업 이중 실패 시 실패 문구가 claude_code 가 되어 그대로 리뷰/테스트됨</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Phase 1 에서 Claude 와 그 백업이 모두 실패(타임아웃/세션 한도)한 상태</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>1. 코딩 요청 2. Phase 1 Claude 타임아웃 -&gt; 백업 투입 -&gt; 백업도 세션 한도로 실패 3. _ask_with_backup 이 "[Claude] 응답을 받지 못했습니다 (백업 ... 도 실패)." 를 반환 4. 이 문구가 claude_code 로 Phase 2 리뷰 프롬프트와 Phase 3 테스트 프롬프트에 "코드" 로 삽입됨. 백업이 아예 없는 경우엔 실패 원문이 그대로 반환돼 답변으로 게시까지 됨</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>원인: modes/coding.py 의 Phase 1 호출부(_start_inner, followup 재개)가 _ask_with_backup 반환값의 성공 여부(needs_replacement)를 확인하지 않고 무조건 Phase 2/3 로 넘겼다. 또한 _ask_with_backup 은 백업 풀이 소진되면 실패 원문을 그대로 돌려줬다. 수정: Phase 1 실패 시 "코드 생성 실패 -&gt; 리뷰/테스트 단계 중단" 을 고지하고 후속 단계 진입을 차단. _ask_with_backup 은 백업이 없어도 실패 원문 대신 정제 문구를 반환하고 needs_replacement 로 실패를 알림</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>코딩 모드 Phase 1 -&gt; Phase 2/3 전이, 백업 풀 소진 경로</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>BE v0.8.19</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>BE v0.8.20</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>병렬 모드에서 백업이 없는 실패 에이전트의 응답 원문이 최종 요약 프롬프트로 유입</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>코딩 병렬 모드에서 한 에이전트가 실패하고 그 백업이 없는 상태</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>1. 코딩 병렬 모드 실행 2. Claude 타임아웃, 백업 풀 소진 3. modes/coding.py:669-670 이 실패 원문을 final_responses 에 그대로 append 4. 678-679 가 그걸 "[Claude 결과]" 로 요약 프롬프트에 삽입 -&gt; Codex 가 타임아웃 문구를 작업 결과로 읽고 요약</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>원인: 백업이 존재할 때만 continue 로 빠져나가고, 백업이 없으면 실패한 에이전트와 그 실패 원문이 그대로 final_agents/final_responses 에 담겼다. 수정: 백업이 없거나 백업까지 실패하면 결과 없이 제외하고 사유를 고지. 전원 실패면 빈 요약을 요청하지 않고 중단</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>코딩 병렬 모드 최종 보고서</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>BE v0.8.19</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>BE v0.8.20</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>최종 보고서 생성이 실패하면 그 실패 원문이 "최종 보고서" 로 방송됨</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>최종 보고서 작성 단계에서 Codex 가 타임아웃/오류로 실패한 상태</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>1. 코딩 모드 실행 2. 마지막 보고서 생성 호출에서 Codex 타임아웃 3. 반환된 "[Codex] 응답 시간 초과 (300초)" 가 그대로 "📋 최종 보고서 (Codex)" 로 broadcast 됨 (병렬 모드도 동일)</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>원인: 보고서 호출 결과의 needs_replacement 를 확인하지 않고 무조건 방송했다. 수정: 실패 시 방송하지 않고 "최종 보고서 생성 실패" 고지로 대체. 아울러 None(호출 실패)과 ""(내용 없는 정상 응답)을 구분하는 _test_summary() 를 도입해 보고서가 둘을 혼동하지 않게 함</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>코딩 모드/병렬 모드 최종 보고서 방송</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>BE v0.8.19</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>BE v0.8.20</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>타임아웃 메시지가 실제보다 60초 적은 "574초" 로 표기되고 한도(600초)도 초과</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>코딩 모드에서 Claude 가 도구 호출 중 60초 이상 무응답인 상태</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>1. 코딩 모드 실행 2. Claude 가 스트리밍 중 장시간 무응답 3. 전체 한도 600초를 넘겨 종료되는데 Slack 에는 "[Claude] 응답 대기 시간 초과 (574초)" 로 게시됨 (실제 경과는 634초)</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>원인: agents/claude.py(및 동형인 gemini.py) 읽기 루프가 elapsed 를 루프 진입 시점에 재고, readline 을 고정 60초 기다린 뒤 그 stale 값을 메시지에 찍었다. 한도 검사도 루프 진입 시점에만 해서 readline_timeout(60초) 만큼 한도를 넘겼다(실효 상한 660초). 수정: readline 대기를 min(STREAM_IDLE_TIMEOUT, 남은 예산) 으로 자르고, 보고 직전 elapsed 를 재측정. 메시지에 한도를 병기(응답 시간 초과 (634초 / 한도 600초)). start_time 도 spawn 전으로 옮겨 spawn/stdin drain 시간을 예산에 포함(Codex 지적 반영)</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>코딩/토론/리서치 전 모드의 스트리밍 타임아웃 메시지 및 실제 상한</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>BE v0.8.20</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>BE v0.8.21</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>같은 timeout 인자가 에이전트마다 다른 예산을 의미 (Codex 300초 vs Claude 660초)</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>1. 코딩 모드에서 timeout=CLI_TIMEOUT_CODING(300) 을 모든 에이전트에 동일하게 전달 2. 실제로는 base(Codex)=300초, Claude=600(+60)초, Gemini=600초/가드 750초로 제각각 3. 한 실행에 "[Claude] 응답 시간 초과 (300초)" 와 "(574초)" 가 동시에 찍힘</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>원인: 스트리밍 구현이 내부에서 timeout 을 조용히 t*2 로 늘렸고 base 구현은 안 늘렸다. 수정: 숨은 배수 제거. timeout 이 곧 예산. 모드별 예산을 상수로 승격 (CLI_TIMEOUT 180-&gt;360, CLI_TIMEOUT_CODING 300-&gt;600, CLI_TIMEOUT_RESEARCH 180 신설). 실효 예산은 의도적으로 조정됨: 코딩 Claude 660-&gt;600(축소), 코딩 Codex 300-&gt;600(확대). Codex 확대는 의도 - 예전엔 절반 예산이라 정상 장시간 작업 중 혼자 먼저 타임아웃 나 불필요하게 백업 교체됐다. 토론 라운드 체감 상한은 420-&gt;360초로 오히려 감소</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>전 모드 에이전트 호출 예산, 백업 교체 빈도</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>BE v0.8.20</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>BE v0.8.21</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>한 에이전트의 타임아웃이 병렬 실행 중인 형제 에이전트의 프로세스까지 kill</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>여러 에이전트가 asyncio.gather 로 병렬 실행 중 (코딩 Phase 3, 리서치 분담 조사)</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>1. 코딩 Phase 3 에서 Codex/Claude/Gemini 가 같은 thread_ts 로 병렬 실행 2. 그 중 하나가 타임아웃 3. _kill_registered_processes() 가 thread_ts 에 등록된 모든 프로세스를 죽여 멀쩡히 돌던 나머지 에이전트도 동반 실패 4. 테스트 결과 0건 -&gt; Codex 가짜 이슈 -&gt; 수정 루프 헛돎</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>원인: cancel.active_processes 가 thread_ts 단위 레지스트리인데 타임아웃 정리가 그걸 그대로 순회해 전부 죽였다. 모든 에이전트는 같은 _current_thread_ts 를 공유한다. 게다가 리서치는 하위질문을 라운드로빈 배정하므로 같은 인스턴스가 동시에 2건을 맡기도 한다(4문항/3에이전트). 수정: contextvars.ContextVar + AgentBase._call_scope() 로 kill 사정거리를 호출 단위로 축소. 사용자 취소(/cancel)는 기존대로 스레드 전체 kill 유지</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>코딩 Phase 3, 리서치 분담 조사, 토론 라운드 (병렬 실행 전 구간)</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>BE v0.8.20</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>BE v0.8.21</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Claude 스트리밍에 외부 가드가 없어 읽기 루프 밖 hang 이 영구 대기</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>stdin drain 이 막히거나 proc.wait() 이 복귀하지 않는 상태</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>1. Claude CLI 가 stdin 을 읽지 않아 파이프 버퍼가 참 2. await proc.stdin.drain() 이 영구 블록 3. 읽기 루프에 진입조차 못 해 내부 데드라인 검사가 발동하지 않음 4. 봇 정지</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>원인: 내부 데드라인은 읽기 루프 안에서만 검사된다. 루프 밖 await(stdin drain, proc.wait)은 그 검사에 도달하지 못한다. Gemini 는 v0.7.3.2 에서 외부 가드를 받았지만 Claude 는 무방비였다. 수정: base.ask_with_progress 가 _stream_once 를 t*STREAM_GUARD_FACTOR(1.25) 로 감싼다. Claude 는 _stream_once 만 오버라이드하도록 정리했고 Codex 는 super() 위임이라 자동 적용. 상한은 정상 t, 병리적 hang 시 t*1.25</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Claude/Codex 스트리밍 호출 (코딩 전 Phase, 토론 라운드)</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>BE v0.8.20</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>BE v0.8.21</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>외부 가드 취소 시 살아있는 CLI 를 죽이기 전에 부산물을 지워 임시 폴더에 파일 누수</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>외부 가드가 발동해 _stream_once 코루틴이 cancel 되는 상태</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>1. 외부 가드(asyncio.wait_for) 타임아웃 2. wait_for 가 내부 Task 를 cancel 하고 그 Task 의 finally 가 먼저 완료됨 3. 그 finally 가 아직 살아있는 CLI 의 -o &lt;tmp&gt;.last.md 부산물과 프롬프트 파일을 삭제 4. 그 뒤에야 호출부 except 가 프로세스를 kill 5. 삭제와 kill 사이에 살아있는 writer 가 파일을 다시 써서 임시 폴더에 남음</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>원인: 정리 순서가 (파일 삭제 -&gt; 프로세스 kill) 이었다. asyncio.wait_for 는 내부 Task 의 finally 가 끝난 뒤에야 호출부로 제어를 넘기므로, 파일 정리 시점에 CLI 가 아직 살아있다. 수정: _kill_if_alive() 를 파일 정리 앞에 배치해 writer 를 먼저 죽인다(kill_process_tree 는 동기 함수라 cancel 중인 finally 안에서도 안전 - 여기서 await 하면 CancelledError 가 재발생해 정리가 중단된다). Codex 교차검증 지적 반영</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>CodexAgent 의 -o 최종 메시지 파일, 전 에이전트의 프롬프트 임시 파일</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>BE v0.8.20</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>BE v0.8.21</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>bug</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>코딩 모드 백업 에이전트가 primary 보다 짧은 예산으로 호출됨</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>primary 에이전트가 타임아웃/오류로 백업 교체가 트리거된 상태</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>1. 코딩 모드에서 primary 가 코딩 예산(600초)을 다 쓰고 타임아웃 2. _ask_with_backup 이 backup.ask(prompt) 를 timeout 인자 없이 호출 3. 백업은 기본 예산(CLI_TIMEOUT)만 받아 primary 보다 짧은 시간 안에 끝내야 함</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>원인: modes/coding.py 의 백업 호출만 timeout 인자를 빠뜨렸다(다른 백업 경로는 CLI_TIMEOUT_CODING 을 넘긴다). primary 가 코딩 예산으로도 못 끝낸 일을 더 짧은 예산으로 시키는 꼴이라 이중 실패(백업도 실패) 확률만 올라간다. 수정: timeout=CLI_TIMEOUT_CODING 명시. 재시도 정책 점검 결과 타임아웃 자체는 재시도하지 않고(같은 예산 재실행은 실패 시간만 2배) 곧바로 백업 교체하되, 백업은 primary 와 같은 예산을 받는 것으로 확정</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>코딩 모드 백업 교체 경로</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>BE v0.8.20</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>BE v0.8.21</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>enhancement</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>에이전트 상태 플래그(timed_out/has_error/last_usage)가 인스턴스 공유라 병렬 호출에 취약</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>리서치가 같은 에이전트 인스턴스를 병렬 호출하는데(라운드로빈 배정: 4문항/3에이전트) timed_out/has_error/last_usage 는 인스턴스 속성이다. 호출별 상태 객체로 분리하거나 호출 결과에 상태를 함께 반환해 공유 플래그 판정을 제거해야 한다.</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>v0.8.21 에서 프로세스 kill 사정거리는 호출 단위로 좁혔으나 상태 플래그는 여전히 인스턴스 공유다. 현재 호출부는 ask() 반환 직후 await 없이 곧바로 플래그를 읽으므로(이벤트 루프가 그 사이에 다른 코루틴을 끼워넣지 못함) 실제 트리거는 확인되지 않았다. 다만 호출부에 await 가 하나만 끼어들면 곧바로 오판(한 호출의 실패가 다른 호출의 백업 교체를 유발)으로 이어지는 구조적 취약점이라 선제 정리가 필요하다. Codex 교차검증 지적 반영</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>리서치 분담 조사, 향후 동일 인스턴스 병렬 호출을 추가하는 모든 경로</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>BE v0.8.21</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L142"/>
+  <dimension ref="A1:L148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8787,6 +8787,366 @@
         </is>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>한 에이전트의 타임아웃이 병렬 실행 중인 형제 에이전트의 CLI 프로세스까지 kill</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>토론/리서치에서 3개 에이전트가 같은 thread_ts 로 병렬 실행 중, 그중 하나가 타임아웃</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>1. 리서치/토론 실행 2. 한 에이전트가 타임아웃 3. base._kill_registered_processes 가 cancel.active_processes[thread_ts] 전체를 kill 4. 답변 중이던 나머지 에이전트도 같이 죽어 '응답 시간 초과' 로 표시됨. 실측: 7/9 리서치 로그에 [Claude-B] 180초 초과와 [Codex-B] 180초 초과가 같은 런에서 동시 발생(조사 1건 유실)</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>원인: _kill_registered_processes 가 이름/주석과 달리 thread_ts 의 모든 프로세스를 돌며 kill. 에이전트들이 thread_ts 를 공유하고 gather 로 병렬 실행되므로 형제 동반 사망. 수정: contextvars 기반 호출 스코프(_call_scope/_register_proc) 도입, 타임아웃 정리는 그 호출이 띄운 프로세스만 kill. /cancel 의 스레드 전체 kill 은 유지. GH #145</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>토론/리서치/코딩 전 모드의 병렬 에이전트 실행</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>BE v0.8.19.1</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>BE v0.8.20</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>같은 timeout 인자가 에이전트마다 다른 예산을 의미 (Codex 300초 vs Claude 660초)</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>1. 코딩 모드 실행(CLI_TIMEOUT_CODING=300) 2. Codex 는 300초에 타임아웃, Claude 는 600초까지 살아있음 3. 한 실행 로그에 '(300초)' 와 '(574초)' 가 함께 찍힘 4. Codex 만 먼저 죽고 그 타임아웃이 형제 kill 유발</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>원인: base=t, Claude=t*2, Gemini=t*2(가드 t*2.5) 로 내부에서 배수를 곱해 같은 인자가 다른 예산을 뜻함. 수정: 숨은 배수 전부 제거(timeout=t = 그 호출의 예산 t초). 실효 예산 유지를 위해 상수 상향: CLI_TIMEOUT 180→360, CLI_TIMEOUT_CODING 300→600. GH #144</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>전 모드 타임아웃 동작, config.py</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>BE v0.8.19.1</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>BE v0.8.20</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>코딩 모드 백업 에이전트가 primary 보다 짧은 예산으로 호출됨</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>코딩 모드에서 primary 가 타임아웃/오류로 백업이 투입되는 상황</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>1. 코딩 모드에서 Claude 가 CLI_TIMEOUT_CODING(300초) 로 실패 2. _ask_with_backup 이 backup.ask(prompt) 를 timeout 없이 호출 → 기본 CLI_TIMEOUT(180초) 3. primary 가 300초로도 못 끝낸 일을 백업이 180초에 처리해야 함 → 이중 실패 확률 상승</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>원인: modes/coding.py 의 백업 호출에 timeout 인자 누락. 수정: timeout=CLI_TIMEOUT_CODING 명시. GH #148</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>코딩 모드 백업 투입 경로</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>BE v0.8.19.1</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>BE v0.8.20</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>리서치가 같은 에이전트 인스턴스에 소주제 2건을 동시 배정해 상태 플래그가 섞임</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>리서치 소주제가 에이전트 수보다 많을 때(RESEARCH_SUBQ_MAX=4, 에이전트 3개)</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>1. 소주제 4개가 3개 에이전트에 라운드로빈 배정 2. 한 인스턴스가 2건을 gather 로 동시 실행 3. timed_out/has_error/last_usage 가 인스턴스 속성이라 서로 덮어씀 4. 멀쩡한 조사가 실패로 판정돼 버려질 수 있음</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>원인: 인스턴스 상태 플래그 + 동일 인스턴스 동시 호출. 수정: _run_assigned() 로 분리해 에이전트 간에는 병렬, 같은 에이전트 안에서는 순차 실행. 에이전트 간 병렬성은 유지. GH #149</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>리서치 모드 분담 조사</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>BE v0.8.19.1</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>BE v0.8.20</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Claude 스트리밍에 외부 가드가 없어 읽기 루프 밖 hang 이 영구 대기</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Claude CLI 가 stdin drain/proc.wait 등 읽기 루프 밖에서 멈추는 경우</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>1. Claude CLI 호출 2. await proc.stdin.drain() 에서 자식이 stdin 을 안 읽어 블록 3. 내부 데드라인은 읽기 루프 안에서만 검사하므로 도달하지 못함 4. 영구 대기(과거 Gemini 33분 hang 과 동일 계열)</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>원인: 읽기 루프 밖 await 에 데드라인 부재. 수정: base.ask_with_progress 가 _stream_once 를 t*GUARD_FACTOR(1.25) 로 감싸고, 가드 발동 시 해당 호출의 프로세스만 정리. Gemini 가드도 t*2.5→t*1.25 로 통일. GH #146</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Claude 계열 에이전트 전 모드</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>BE v0.8.19.1</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>BE v0.8.20</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>타임아웃 메시지가 실제보다 최대 60초 적게 표기되고 한도도 초과</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Claude 스트리밍이 타임아웃되는 경우</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>1. 코딩 모드에서 Claude 타임아웃 2. Slack 에 '[Claude] 응답 대기 시간 초과 (574초)' 표기 3. 실제 경과는 634초 4. 한도 검사도 루프 진입 시점에만 해서 실효 상한이 예산+60초</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>원인: 루프 진입 시점에 잰 elapsed 를 60초 readline 대기 후 그대로 보고. 수정: readline 대기를 min(60, 남은 예산) 으로 자르고 보고 직전 elapsed 재측정. start_time 을 spawn 전으로 이동해 spawn/drain 도 예산에 포함. GH #143</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Claude 타임아웃 메시지/실효 한도</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>BE v0.8.19.1</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>BE v0.8.20</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L148"/>
+  <dimension ref="A1:L149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9147,6 +9147,70 @@
         </is>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>agy 콘솔 창 깜빡임 (이슈 #112 wontfix 재조사 후 해결)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>GEMINI_CLI_BINARY=agy + 봇이 대화형 세션(로그인 상태)에서 가동</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>1. 토론/리서치 채널에 질문 전송
+2. agy 호출 시 cmd 콘솔 창이 잠깐 떴다가 사라짐(깜빡임)
+(이슈 #112 는 '호출마다' 라고 기록했으나 실측 결과 15분에 한 번)</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>원인(실측 확정): agy 는 ~/.gemini/antigravity-cli/last_check.timestamp 기준 **15분 쿨다운**으로 업데이트를 체크한다(cli.log: 'auto_updater.go:207] Last check was less than 15 minutes ago, skipping update'). 쿨다운이 지나면 detached 손자 'agy --bg-updater' -&gt; 'agy --version' 을 spawn 하고, 그 'agy --version' 이 소유한 PseudoConsoleWindow 가 대화형 데스크톱에 표시된다(Win32 GetWindowThreadProcessId 로 창 소유 프로세스 pid 까지 확인). agy 1.1.2 에서도 그대로이며 1.0.16-&gt;1.1.2 체인지로그에 관련 수정 없음.
+수정: agents/gemini.py 에 _suppress_agy_updater() 추가. agy 를 띄우기 직전에 타임스탬프를 **현재 시각**으로 갱신하면 agy 가 항상 쿨다운으로 판정해 업데이터를 아예 spawn 하지 않는다. 이슈 #112 는 타임스탬프 '미래화' 를 시도했다가 agy 가 리셋해 실패했는데, 미래 시각은 이상값이라 되돌려진 것으로 보인다(현재 시각은 정상값이라 쿨다운에 그대로 걸린다). _run_cli 와 _run_progress_once 양쪽에 적용(토론/코딩은 후자를 탄다 - Codex 교차검증 발견). temp+os.replace 로 원자적 쓰기(agy 가 빈 파일을 읽으면 오히려 업데이터가 뜬다), temp 이름에 uuid(교차 스레드 충돌 방지), best-effort(실패해도 봇을 죽이지 않음).
+검증: 단위 9건 + 전체 487 통과. E2E 실측 - 대조군 창 1개 vs 억제 3회 모두 창 0개.</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>agy 사용 시 모든 에이전트 호출(토론/코딩/리서치), Windows 대화형 세션. 부작용: agy 자동 업데이트 영구 스킵(이미 AGY_CLI_DISABLE_AUTO_UPDATE 로 끄고 있어 의도와 부합, 업데이트는 수동 `agy update`)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>BE v0.8.20</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>BE v0.8.22</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -551,7 +551,7 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>트래커</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>제안 GH번호</t>
+          <t>제안 트래커</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>GH 제목</t>
+          <t>트래커 제목</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -6138,6 +6138,16 @@
           <t>enhancement</t>
         </is>
       </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr">
         <is>
           <t>Slack 첨부 이미지 분석 지원 (Claude/Gemini Vision)</t>
@@ -6196,6 +6206,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr">
         <is>
           <t>이미지 첨부 분석을 SDK 직호출로 잘못 구현 → CLI prompt 첨부로 정정</t>
@@ -6259,6 +6279,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr">
         <is>
           <t>텍스트+이미지 한 번에 입력 시 봇 무반응</t>
@@ -6541,6 +6571,16 @@
           <t>enhancement</t>
         </is>
       </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr">
         <is>
           <t>Gemini 차트 이미지 종목 오인 방지 가드</t>
@@ -6602,6 +6642,16 @@
       <c r="C87" t="inlineStr">
         <is>
           <t>bug</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>backend</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6672,6 +6722,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr">
         <is>
           <t>토론 교착 감지(_is_stalemate) 사실상 미발동으로 합의 실패 시 최대 라운드까지 낭비</t>
@@ -6738,6 +6798,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr">
         <is>
           <t>백업 풀 비대칭 + 이중 장애 시 에이전트 다양성 붕괴 및 동일 인스턴스 중복</t>
@@ -6804,6 +6874,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr">
         <is>
           <t>_parse_consensus JSON 파싱 실패 시 무음 None 반환으로 합의 누락</t>
@@ -6870,6 +6950,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr">
         <is>
           <t>최종 통합문을 self.agents[0] 단독 생성하여 교체된 백업 모델로 편향</t>
@@ -6935,6 +7025,16 @@
           <t>enhancement</t>
         </is>
       </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr">
         <is>
           <t>난이도 기반 라운드 라우팅(단순 조기 종료, 복잡 최소 라운드 확보)</t>
@@ -7059,6 +7159,16 @@
       <c r="C94" t="inlineStr">
         <is>
           <t>bug</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>backend</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -7196,6 +7306,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F96" t="inlineStr">
         <is>
           <t>agy 호출이 cmd /c 로 감싸져 prompt 메타문자가 셸 파싱됨 + argv 길이 한계 미가드</t>
@@ -7476,6 +7596,16 @@
           <t>enhancement</t>
         </is>
       </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F100" t="inlineStr">
         <is>
           <t>PDF 첨부 지원 추가 (이미지에 더해 PDF 도 각 CLI read 도구로 처리) + images → attachments 전체 리네이밍</t>
@@ -7532,6 +7662,16 @@
       <c r="C101" t="inlineStr">
         <is>
           <t>bug</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>backend</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -7600,6 +7740,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr">
         <is>
           <t>v0.7.5 자체 회귀: slack_bot.py 의 os import 누락으로 PDF/이미지 첨부 시 _runner NameError 무응답</t>
@@ -7666,6 +7816,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr">
         <is>
           <t>토론 합의된 답변이 모델 답변 대신 'API Error: 500 Internal server error' 에러 문구로 방송됨</t>
@@ -7731,6 +7891,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F104" t="inlineStr">
         <is>
           <t>Gemini 매 발언 첫 줄에 'True color (24-bit) support not detected' 터미널 경고 누출</t>
@@ -7795,6 +7965,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr">
         <is>
           <t>토론 결론의 "미해결 쟁점"이 각 에이전트 요약/합의된 답변과 중복 (disagreements 필드 미사용 dead data)</t>
@@ -7860,6 +8040,16 @@
           <t>enhancement</t>
         </is>
       </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
           <t>agy `-p` stdout 미출력 버그(#76) 우회 - 디스크 transcript 에서 trace 토큰으로 응답 복구</t>
@@ -8621,6 +8811,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr">
         <is>
           <t>리서치 모드, 교차검증이 찾은 교정 사실 무시 + 긴 링크 분할로 출력 깨짐</t>
@@ -8684,6 +8884,16 @@
           <t>enhancement</t>
         </is>
       </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr">
         <is>
           <t>리서치 모드 1차 출처 정독 + 결론 정교화 재설계</t>
@@ -8742,6 +8952,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr">
         <is>
           <t>리서치 분해가 부모 질문·제약을 하위질문에 누락 (제약 위반 답·조사불가)</t>
@@ -8805,6 +9025,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr">
         <is>
           <t>리서치 종합 에이전트 실패 시 raw 에러 문자열을 종합 답변으로 방송</t>
@@ -8868,6 +9098,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr">
         <is>
           <t>리서치 백업 에이전트 타임아웃성 응답이 finding 으로 리포트에 노출</t>
@@ -8931,6 +9171,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F122" t="inlineStr">
         <is>
           <t>토론 모드 cwd 미설정으로 Codex 가 외부 경로 평가 시 차단</t>
@@ -8994,6 +9244,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F123" t="inlineStr">
         <is>
           <t>!bot restart 1회에 봇이 5중 spawn (재시작 재진입/중복)</t>
@@ -9057,6 +9317,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F124" t="inlineStr">
         <is>
           <t>mutex 전환 후 watchdog_guard 가 3분마다 헛 재기동(churn)</t>
@@ -9120,6 +9390,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F125" t="inlineStr">
         <is>
           <t>Claude 세션 한도 초과 메시지가 백업 미투입 + '합의된 답변'으로 방송</t>
@@ -9183,6 +9463,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Minor (테스트 전용, 제품 기능 영향 없음. 개발 머신에서 false 실패 → CI/개발 신뢰성 저하)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>etc</t>
+        </is>
+      </c>
       <c r="F126" t="inlineStr">
         <is>
           <t>TestBinarySelection 4건이 dev .env 의 GEMINI_CLI_BINARY=agy 누수로 실패 (테스트 격리)</t>
@@ -9246,6 +9536,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>etc</t>
+        </is>
+      </c>
       <c r="F127" t="inlineStr">
         <is>
           <t>!bot restart 한 번에 봇이 세션 수만큼(4중) 중복 spawn (크로스세션 워치독 중복)</t>
@@ -9309,6 +9609,16 @@
           <t>enhancement</t>
         </is>
       </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>etc</t>
+        </is>
+      </c>
       <c r="F128" t="inlineStr">
         <is>
           <t>워치독 크로스세션 단일 인스턴스 원자적 봉합 (LockFileEx)</t>
@@ -9873,6 +10183,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F136" t="inlineStr">
         <is>
           <t>합의 조기 종료 불가: 어휘 발산 판정이 상시 True 라 만장일치에도 교전 라운드 강제</t>
@@ -9936,6 +10256,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F137" t="inlineStr">
         <is>
           <t>Codex 툴콜 preamble('먼저 ~를 확인하겠습니다')이 최종 답변 앞에 노출</t>
@@ -10067,6 +10397,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F139" t="inlineStr">
         <is>
           <t>백업까지 실패하는 이중 장애에서 백업의 에러 원문이 답변으로 게시됨</t>
@@ -10203,6 +10543,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F141" t="inlineStr">
         <is>
           <t>codex -o 최종 메시지 파일 경로를 인스턴스 필드에 저장해 동시 호출 간 충돌/누수</t>
@@ -10339,6 +10689,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F143" t="inlineStr">
         <is>
           <t>한 에이전트의 타임아웃이 병렬 실행 중인 형제 에이전트의 CLI 프로세스까지 kill</t>
@@ -10548,6 +10908,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F146" t="inlineStr">
         <is>
           <t>리서치가 같은 에이전트 인스턴스에 소주제 2건을 동시 배정해 상태 플래그가 섞임</t>
@@ -10684,6 +11054,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F148" t="inlineStr">
         <is>
           <t>타임아웃 메시지가 실제보다 최대 60초 적게 표기되고 한도도 초과</t>
@@ -10831,6 +11211,11 @@
           <t>외부 가드가 취소할 때 CLI 프로세스가 아직 살아 있는데 부산물을 먼저 지워 임시 폴더에 파일이 남는다</t>
         </is>
       </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>외부 가드가 발동해 `_stream_once` 코루틴이 cancel 되는 상태</t>
+        </is>
+      </c>
       <c r="N150" t="inlineStr">
         <is>
           <t>코드 리뷰</t>
@@ -10839,6 +11224,21 @@
       <c r="O150" t="inlineStr">
         <is>
           <t>GitHub 이슈 원문에서 역으로 채운 행이다. 등록 당시 엑셀 기록이 빠졌다.</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>CodexAgent 의 `-o` 최종 메시지 파일, 전 에이전트의 프롬프트 임시 파일</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>BE v0.8.20</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>BE v0.8.21 (커밋: 18fb6a8)</t>
         </is>
       </c>
       <c r="T150" t="inlineStr">

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -422,7 +422,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:V150"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -7533,6 +7533,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>critical</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr">
         <is>
           <t>v0.7.3.2 핫픽스 누락: _run_progress_once L293 _gemini_concurrency 잔존 + cancel cleanup 부재</t>
@@ -7576,6 +7586,11 @@
           <t>완료</t>
         </is>
       </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SYM-11</t>
+        </is>
+      </c>
       <c r="V99" t="inlineStr">
         <is>
           <t>Block</t>
@@ -11127,6 +11142,16 @@
           <t>bug</t>
         </is>
       </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>minor</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
       <c r="F149" t="inlineStr">
         <is>
           <t>agy 콘솔 창 깜빡임 (이슈 #112 wontfix 재조사 후 해결)</t>
@@ -11169,6 +11194,11 @@
       <c r="T149" t="inlineStr">
         <is>
           <t>완료</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>SYM-12</t>
         </is>
       </c>
       <c r="V149" t="inlineStr">
